--- a/df_state.xlsx
+++ b/df_state.xlsx
@@ -124,6 +124,289 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -304,7 +587,7 @@
         <v>20260526</v>
       </c>
       <c r="K2" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -397,7 +680,7 @@
         <v>20260526</v>
       </c>
       <c r="K3" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L3" t="n">
         <v>1200</v>
@@ -490,7 +773,7 @@
         <v>20260526</v>
       </c>
       <c r="K4" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -595,7 +878,7 @@
         <v>20260526</v>
       </c>
       <c r="K5" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L5" t="n">
         <v>3600</v>
@@ -700,7 +983,7 @@
         <v>20260526</v>
       </c>
       <c r="K6" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -793,7 +1076,7 @@
         <v>20260526</v>
       </c>
       <c r="K7" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -886,7 +1169,7 @@
         <v>20260526</v>
       </c>
       <c r="K8" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -979,7 +1262,7 @@
         <v>20260526</v>
       </c>
       <c r="K9" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1072,7 +1355,7 @@
         <v>20260526</v>
       </c>
       <c r="K10" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L10" t="n">
         <v>900</v>
@@ -1165,13 +1448,13 @@
         <v>20260526</v>
       </c>
       <c r="K11" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1180,7 +1463,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>16:25:00</t>
+          <t>16:55:00</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1270,13 +1553,13 @@
         <v>20260526</v>
       </c>
       <c r="K12" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L12" t="n">
         <v>3000</v>
       </c>
       <c r="M12" t="n">
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1285,7 +1568,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>18:11:00</t>
+          <t>18:41:00</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1375,7 +1658,7 @@
         <v>20260526</v>
       </c>
       <c r="K13" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1468,7 +1751,7 @@
         <v>20260526</v>
       </c>
       <c r="K14" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1561,7 +1844,7 @@
         <v>20260526</v>
       </c>
       <c r="K15" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1654,7 +1937,7 @@
         <v>20260526</v>
       </c>
       <c r="K16" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1747,7 +2030,7 @@
         <v>20260526</v>
       </c>
       <c r="K17" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1840,7 +2123,7 @@
         <v>20260526</v>
       </c>
       <c r="K18" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1945,7 +2228,7 @@
         <v>20260526</v>
       </c>
       <c r="K19" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2050,7 +2333,7 @@
         <v>20260526</v>
       </c>
       <c r="K20" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2155,7 +2438,7 @@
         <v>20260526</v>
       </c>
       <c r="K21" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2260,7 +2543,7 @@
         <v>20260526</v>
       </c>
       <c r="K22" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2365,7 +2648,7 @@
         <v>20260526</v>
       </c>
       <c r="K23" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2470,7 +2753,7 @@
         <v>20260526</v>
       </c>
       <c r="K24" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2575,7 +2858,7 @@
         <v>20260526</v>
       </c>
       <c r="K25" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2680,7 +2963,7 @@
         <v>20260526</v>
       </c>
       <c r="K26" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L26" t="n">
         <v>300</v>
@@ -2785,7 +3068,7 @@
         <v>20260526</v>
       </c>
       <c r="K27" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L27" t="n">
         <v>300</v>
@@ -2890,7 +3173,7 @@
         <v>20260526</v>
       </c>
       <c r="K28" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L28" t="n">
         <v>300</v>
@@ -2995,7 +3278,7 @@
         <v>20260526</v>
       </c>
       <c r="K29" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L29" t="n">
         <v>300</v>
@@ -3100,7 +3383,7 @@
         <v>20260526</v>
       </c>
       <c r="K30" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3205,7 +3488,7 @@
         <v>20260526</v>
       </c>
       <c r="K31" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3310,7 +3593,7 @@
         <v>20260526</v>
       </c>
       <c r="K32" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3415,13 +3698,13 @@
         <v>20260526</v>
       </c>
       <c r="K33" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3430,7 +3713,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>15:37:00</t>
+          <t>16:27:00</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -3520,29 +3803,29 @@
         <v>20260526</v>
       </c>
       <c r="K34" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L34" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="M34" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>16:04:00</t>
+          <t>16:54:00</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>16:07:00</t>
+          <t>16:57:00</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="Q34" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -3625,29 +3908,29 @@
         <v>20260526</v>
       </c>
       <c r="K35" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L35" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="M35" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>16:34:00</t>
+          <t>17:24:00</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>16:34:00</t>
+          <t>17:24:00</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="Q35" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -3730,7 +4013,7 @@
         <v>20260526</v>
       </c>
       <c r="K36" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3835,7 +4118,7 @@
         <v>20260526</v>
       </c>
       <c r="K37" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L37" t="n">
         <v>600</v>
@@ -3940,7 +4223,7 @@
         <v>20260526</v>
       </c>
       <c r="K38" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L38" t="n">
         <v>6600</v>
@@ -4045,7 +4328,7 @@
         <v>20260526</v>
       </c>
       <c r="K39" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L39" t="n">
         <v>7800</v>
@@ -4150,7 +4433,7 @@
         <v>20260526</v>
       </c>
       <c r="K40" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L40" t="n">
         <v>7800</v>
@@ -4255,7 +4538,7 @@
         <v>20260526</v>
       </c>
       <c r="K41" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L41" t="n">
         <v>7800</v>
@@ -4360,7 +4643,7 @@
         <v>20260526</v>
       </c>
       <c r="K42" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L42" t="n">
         <v>7800</v>
@@ -4465,7 +4748,7 @@
         <v>20260526</v>
       </c>
       <c r="K43" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L43" t="n">
         <v>7800</v>
@@ -4570,7 +4853,7 @@
         <v>20260526</v>
       </c>
       <c r="K44" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L44" t="n">
         <v>7800</v>
@@ -4675,7 +4958,7 @@
         <v>20260526</v>
       </c>
       <c r="K45" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L45" t="n">
         <v>7800</v>
@@ -4780,7 +5063,7 @@
         <v>20260526</v>
       </c>
       <c r="K46" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L46" t="n">
         <v>7800</v>
@@ -4885,7 +5168,7 @@
         <v>20260526</v>
       </c>
       <c r="K47" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L47" t="n">
         <v>7800</v>
@@ -4990,7 +5273,7 @@
         <v>20260526</v>
       </c>
       <c r="K48" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L48" t="n">
         <v>7800</v>
@@ -5095,7 +5378,7 @@
         <v>20260526</v>
       </c>
       <c r="K49" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L49" t="n">
         <v>7800</v>
@@ -5200,7 +5483,7 @@
         <v>20260526</v>
       </c>
       <c r="K50" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L50" t="n">
         <v>7800</v>
@@ -5305,7 +5588,7 @@
         <v>20260526</v>
       </c>
       <c r="K51" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L51" t="n">
         <v>7800</v>
@@ -5410,7 +5693,7 @@
         <v>20260526</v>
       </c>
       <c r="K52" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L52" t="n">
         <v>7800</v>
@@ -5515,7 +5798,7 @@
         <v>20260526</v>
       </c>
       <c r="K53" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -5608,7 +5891,7 @@
         <v>20260526</v>
       </c>
       <c r="K54" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L54" t="n">
         <v>300</v>
@@ -5701,7 +5984,7 @@
         <v>20260526</v>
       </c>
       <c r="K55" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -5794,7 +6077,7 @@
         <v>20260526</v>
       </c>
       <c r="K56" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -5887,7 +6170,7 @@
         <v>20260526</v>
       </c>
       <c r="K57" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -5980,7 +6263,7 @@
         <v>20260526</v>
       </c>
       <c r="K58" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -6073,7 +6356,7 @@
         <v>20260526</v>
       </c>
       <c r="K59" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -6166,7 +6449,7 @@
         <v>20260526</v>
       </c>
       <c r="K60" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -6259,7 +6542,7 @@
         <v>20260526</v>
       </c>
       <c r="K61" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -6352,7 +6635,7 @@
         <v>20260526</v>
       </c>
       <c r="K62" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -6445,7 +6728,7 @@
         <v>20260526</v>
       </c>
       <c r="K63" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -6550,7 +6833,7 @@
         <v>20260526</v>
       </c>
       <c r="K64" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L64" t="n">
         <v>7800</v>
@@ -6655,7 +6938,7 @@
         <v>20260526</v>
       </c>
       <c r="K65" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L65" t="n">
         <v>7800</v>
@@ -6760,7 +7043,7 @@
         <v>20260526</v>
       </c>
       <c r="K66" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L66" t="n">
         <v>7800</v>
@@ -6865,7 +7148,7 @@
         <v>20260526</v>
       </c>
       <c r="K67" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L67" t="n">
         <v>7200</v>
@@ -6970,7 +7253,7 @@
         <v>20260526</v>
       </c>
       <c r="K68" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L68" t="n">
         <v>7200</v>
@@ -7075,7 +7358,7 @@
         <v>20260526</v>
       </c>
       <c r="K69" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L69" t="n">
         <v>7800</v>
@@ -7180,13 +7463,13 @@
         <v>20260526</v>
       </c>
       <c r="K70" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L70" t="n">
         <v>7800</v>
       </c>
       <c r="M70" t="n">
-        <v>10800</v>
+        <v>12600</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -7195,7 +7478,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>15:54:00</t>
+          <t>16:24:00</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -7285,29 +7568,29 @@
         <v>20260526</v>
       </c>
       <c r="K71" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L71" t="n">
-        <v>10800</v>
+        <v>13200</v>
       </c>
       <c r="M71" t="n">
-        <v>10800</v>
+        <v>12600</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>16:43:00</t>
+          <t>17:23:00</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>16:43:00</t>
+          <t>17:13:00</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>10800</v>
+        <v>13200</v>
       </c>
       <c r="Q71" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -7390,7 +7673,7 @@
         <v>20260526</v>
       </c>
       <c r="K72" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -7483,7 +7766,7 @@
         <v>20260526</v>
       </c>
       <c r="K73" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -7576,7 +7859,7 @@
         <v>20260526</v>
       </c>
       <c r="K74" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L74" t="n">
         <v>300</v>
@@ -7669,7 +7952,7 @@
         <v>20260526</v>
       </c>
       <c r="K75" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L75" t="n">
         <v>300</v>
@@ -7762,29 +8045,29 @@
         <v>20260526</v>
       </c>
       <c r="K76" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>16:38:00</t>
+          <t>16:48:00</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>16:41:00</t>
+          <t>16:51:00</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -7855,29 +8138,29 @@
         <v>20260526</v>
       </c>
       <c r="K77" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>17:40:00</t>
+          <t>17:45:00</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>17:50:00</t>
+          <t>17:55:00</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -7948,29 +8231,29 @@
         <v>20260526</v>
       </c>
       <c r="K78" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>18:17:00</t>
+          <t>18:22:00</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>18:22:00</t>
+          <t>18:27:00</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -8041,29 +8324,29 @@
         <v>20260526</v>
       </c>
       <c r="K79" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>18:44:00</t>
+          <t>18:49:00</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>18:47:00</t>
+          <t>18:52:00</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -8134,29 +8417,29 @@
         <v>20260526</v>
       </c>
       <c r="K80" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>19:09:00</t>
+          <t>19:14:00</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>19:12:00</t>
+          <t>19:17:00</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -8227,29 +8510,29 @@
         <v>20260526</v>
       </c>
       <c r="K81" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>19:41:00</t>
+          <t>19:46:00</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>19:44:00</t>
+          <t>19:49:00</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -8320,29 +8603,29 @@
         <v>20260526</v>
       </c>
       <c r="K82" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>20:13:00</t>
+          <t>20:18:00</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>20:21:00</t>
+          <t>20:26:00</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
@@ -8413,29 +8696,29 @@
         <v>20260526</v>
       </c>
       <c r="K83" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>21:09:00</t>
+          <t>21:14:00</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>21:09:00</t>
+          <t>21:14:00</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
@@ -8506,7 +8789,7 @@
         <v>20260526</v>
       </c>
       <c r="K84" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -8599,7 +8882,7 @@
         <v>20260526</v>
       </c>
       <c r="K85" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -8692,7 +8975,7 @@
         <v>20260526</v>
       </c>
       <c r="K86" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -8785,7 +9068,7 @@
         <v>20260526</v>
       </c>
       <c r="K87" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -8878,7 +9161,7 @@
         <v>20260526</v>
       </c>
       <c r="K88" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L88" t="n">
         <v>300</v>
@@ -8971,7 +9254,7 @@
         <v>20260526</v>
       </c>
       <c r="K89" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L89" t="n">
         <v>300</v>
@@ -9064,7 +9347,7 @@
         <v>20260526</v>
       </c>
       <c r="K90" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L90" t="n">
         <v>300</v>
@@ -9157,7 +9440,7 @@
         <v>20260526</v>
       </c>
       <c r="K91" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L91" t="n">
         <v>300</v>
@@ -9250,7 +9533,7 @@
         <v>20260526</v>
       </c>
       <c r="K92" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L92" t="n">
         <v>600</v>
@@ -9343,7 +9626,7 @@
         <v>20260526</v>
       </c>
       <c r="K93" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L93" t="n">
         <v>600</v>
@@ -9436,7 +9719,7 @@
         <v>20260526</v>
       </c>
       <c r="K94" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L94" t="n">
         <v>600</v>
@@ -9529,7 +9812,7 @@
         <v>20260526</v>
       </c>
       <c r="K95" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -9622,7 +9905,7 @@
         <v>20260526</v>
       </c>
       <c r="K96" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -9715,7 +9998,7 @@
         <v>20260526</v>
       </c>
       <c r="K97" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -9808,7 +10091,7 @@
         <v>20260526</v>
       </c>
       <c r="K98" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -9901,7 +10184,7 @@
         <v>20260526</v>
       </c>
       <c r="K99" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -9994,7 +10277,7 @@
         <v>20260526</v>
       </c>
       <c r="K100" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -10087,7 +10370,7 @@
         <v>20260526</v>
       </c>
       <c r="K101" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -10180,7 +10463,7 @@
         <v>20260526</v>
       </c>
       <c r="K102" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L102" t="n">
         <v>600</v>
@@ -10273,7 +10556,7 @@
         <v>20260526</v>
       </c>
       <c r="K103" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -10378,7 +10661,7 @@
         <v>20260526</v>
       </c>
       <c r="K104" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -10483,7 +10766,7 @@
         <v>20260526</v>
       </c>
       <c r="K105" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L105" t="n">
         <v>3600</v>
@@ -10588,7 +10871,7 @@
         <v>20260526</v>
       </c>
       <c r="K106" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -10681,7 +10964,7 @@
         <v>20260526</v>
       </c>
       <c r="K107" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -10774,7 +11057,7 @@
         <v>20260526</v>
       </c>
       <c r="K108" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -10867,7 +11150,7 @@
         <v>20260526</v>
       </c>
       <c r="K109" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -10960,7 +11243,7 @@
         <v>20260526</v>
       </c>
       <c r="K110" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -11053,7 +11336,7 @@
         <v>20260526</v>
       </c>
       <c r="K111" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L111" t="n">
         <v>1500</v>
@@ -11146,7 +11429,7 @@
         <v>20260526</v>
       </c>
       <c r="K112" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -11239,7 +11522,7 @@
         <v>20260526</v>
       </c>
       <c r="K113" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L113" t="n">
         <v>1200</v>
@@ -11332,7 +11615,7 @@
         <v>20260526</v>
       </c>
       <c r="K114" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L114" t="n">
         <v>900</v>
@@ -11425,7 +11708,7 @@
         <v>20260526</v>
       </c>
       <c r="K115" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -11518,7 +11801,7 @@
         <v>20260526</v>
       </c>
       <c r="K116" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -11611,7 +11894,7 @@
         <v>20260526</v>
       </c>
       <c r="K117" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L117" t="n">
         <v>300</v>
@@ -11704,7 +11987,7 @@
         <v>20260526</v>
       </c>
       <c r="K118" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -11797,7 +12080,7 @@
         <v>20260526</v>
       </c>
       <c r="K119" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -11890,7 +12173,7 @@
         <v>20260526</v>
       </c>
       <c r="K120" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -11983,7 +12266,7 @@
         <v>20260526</v>
       </c>
       <c r="K121" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -12076,7 +12359,7 @@
         <v>20260526</v>
       </c>
       <c r="K122" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -12169,7 +12452,7 @@
         <v>20260526</v>
       </c>
       <c r="K123" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -12262,7 +12545,7 @@
         <v>20260526</v>
       </c>
       <c r="K124" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -12355,7 +12638,7 @@
         <v>20260526</v>
       </c>
       <c r="K125" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -12448,7 +12731,7 @@
         <v>20260526</v>
       </c>
       <c r="K126" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -12541,7 +12824,7 @@
         <v>20260526</v>
       </c>
       <c r="K127" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -12634,7 +12917,7 @@
         <v>20260526</v>
       </c>
       <c r="K128" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -12727,7 +13010,7 @@
         <v>20260526</v>
       </c>
       <c r="K129" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -12820,7 +13103,7 @@
         <v>20260526</v>
       </c>
       <c r="K130" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -12913,7 +13196,7 @@
         <v>20260526</v>
       </c>
       <c r="K131" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -13006,7 +13289,7 @@
         <v>20260526</v>
       </c>
       <c r="K132" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -13099,7 +13382,7 @@
         <v>20260526</v>
       </c>
       <c r="K133" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -13192,7 +13475,7 @@
         <v>20260526</v>
       </c>
       <c r="K134" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -13285,7 +13568,7 @@
         <v>20260526</v>
       </c>
       <c r="K135" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -13378,7 +13661,7 @@
         <v>20260526</v>
       </c>
       <c r="K136" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -13471,29 +13754,29 @@
         <v>20260526</v>
       </c>
       <c r="K137" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
+          <t>17:57:00</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
           <t>17:37:00</t>
         </is>
       </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>17:37:00</t>
-        </is>
-      </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R137" t="inlineStr">
         <is>
@@ -13564,7 +13847,7 @@
         <v>20260526</v>
       </c>
       <c r="K138" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -13657,7 +13940,7 @@
         <v>20260526</v>
       </c>
       <c r="K139" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -13750,7 +14033,7 @@
         <v>20260526</v>
       </c>
       <c r="K140" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -13843,7 +14126,7 @@
         <v>20260526</v>
       </c>
       <c r="K141" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -13936,7 +14219,7 @@
         <v>20260526</v>
       </c>
       <c r="K142" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -14029,7 +14312,7 @@
         <v>20260526</v>
       </c>
       <c r="K143" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -14122,7 +14405,7 @@
         <v>20260526</v>
       </c>
       <c r="K144" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -14215,7 +14498,7 @@
         <v>20260526</v>
       </c>
       <c r="K145" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -14308,7 +14591,7 @@
         <v>20260526</v>
       </c>
       <c r="K146" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -14401,7 +14684,7 @@
         <v>20260526</v>
       </c>
       <c r="K147" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -14494,7 +14777,7 @@
         <v>20260526</v>
       </c>
       <c r="K148" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -14587,7 +14870,7 @@
         <v>20260526</v>
       </c>
       <c r="K149" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -14680,7 +14963,7 @@
         <v>20260526</v>
       </c>
       <c r="K150" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -14785,7 +15068,7 @@
         <v>20260526</v>
       </c>
       <c r="K151" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -14890,7 +15173,7 @@
         <v>20260526</v>
       </c>
       <c r="K152" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L152" t="n">
         <v>900</v>
@@ -14995,7 +15278,7 @@
         <v>20260526</v>
       </c>
       <c r="K153" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L153" t="n">
         <v>900</v>
@@ -15100,13 +15383,13 @@
         <v>20260526</v>
       </c>
       <c r="K154" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="N154" t="inlineStr">
         <is>
@@ -15115,7 +15398,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>16:37:00</t>
+          <t>17:07:00</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -15205,7 +15488,7 @@
         <v>20260526</v>
       </c>
       <c r="K155" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L155" t="n">
         <v>3000</v>
@@ -15310,7 +15593,7 @@
         <v>20260526</v>
       </c>
       <c r="K156" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L156" t="n">
         <v>3000</v>
@@ -15415,7 +15698,7 @@
         <v>20260526</v>
       </c>
       <c r="K157" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -15508,7 +15791,7 @@
         <v>20260526</v>
       </c>
       <c r="K158" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -15601,7 +15884,7 @@
         <v>20260526</v>
       </c>
       <c r="K159" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -15694,7 +15977,7 @@
         <v>20260526</v>
       </c>
       <c r="K160" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -15787,7 +16070,7 @@
         <v>20260526</v>
       </c>
       <c r="K161" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -15880,7 +16163,7 @@
         <v>20260526</v>
       </c>
       <c r="K162" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -15973,7 +16256,7 @@
         <v>20260526</v>
       </c>
       <c r="K163" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -16066,7 +16349,7 @@
         <v>20260526</v>
       </c>
       <c r="K164" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -16159,7 +16442,7 @@
         <v>20260526</v>
       </c>
       <c r="K165" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -16252,7 +16535,7 @@
         <v>20260526</v>
       </c>
       <c r="K166" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -16345,7 +16628,7 @@
         <v>20260526</v>
       </c>
       <c r="K167" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -16371,11 +16654,11 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T167" t="b">
         <v>0</v>
@@ -16438,7 +16721,7 @@
         <v>20260526</v>
       </c>
       <c r="K168" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -16464,11 +16747,11 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T168" t="b">
         <v>0</v>
@@ -16531,7 +16814,7 @@
         <v>20260526</v>
       </c>
       <c r="K169" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -16557,11 +16840,11 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T169" t="b">
         <v>0</v>
@@ -16624,7 +16907,7 @@
         <v>20260526</v>
       </c>
       <c r="K170" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -16717,7 +17000,7 @@
         <v>20260526</v>
       </c>
       <c r="K171" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -16810,7 +17093,7 @@
         <v>20260526</v>
       </c>
       <c r="K172" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -16903,7 +17186,7 @@
         <v>20260526</v>
       </c>
       <c r="K173" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -16996,7 +17279,7 @@
         <v>20260526</v>
       </c>
       <c r="K174" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -17089,7 +17372,7 @@
         <v>20260526</v>
       </c>
       <c r="K175" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -17182,7 +17465,7 @@
         <v>20260526</v>
       </c>
       <c r="K176" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -17275,7 +17558,7 @@
         <v>20260526</v>
       </c>
       <c r="K177" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -17368,7 +17651,7 @@
         <v>20260526</v>
       </c>
       <c r="K178" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -17461,7 +17744,7 @@
         <v>20260526</v>
       </c>
       <c r="K179" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L179" t="n">
         <v>300</v>
@@ -17554,7 +17837,7 @@
         <v>20260526</v>
       </c>
       <c r="K180" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L180" t="n">
         <v>300</v>
@@ -17647,7 +17930,7 @@
         <v>20260526</v>
       </c>
       <c r="K181" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -17740,7 +18023,7 @@
         <v>20260526</v>
       </c>
       <c r="K182" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -17833,7 +18116,7 @@
         <v>20260526</v>
       </c>
       <c r="K183" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -17926,7 +18209,7 @@
         <v>20260526</v>
       </c>
       <c r="K184" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -18019,7 +18302,7 @@
         <v>20260526</v>
       </c>
       <c r="K185" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -18112,7 +18395,7 @@
         <v>20260526</v>
       </c>
       <c r="K186" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -18205,7 +18488,7 @@
         <v>20260526</v>
       </c>
       <c r="K187" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -18298,7 +18581,7 @@
         <v>20260526</v>
       </c>
       <c r="K188" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -18391,7 +18674,7 @@
         <v>20260526</v>
       </c>
       <c r="K189" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L189" t="n">
         <v>1800</v>
@@ -18484,7 +18767,7 @@
         <v>20260526</v>
       </c>
       <c r="K190" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -18577,7 +18860,7 @@
         <v>20260526</v>
       </c>
       <c r="K191" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -18670,7 +18953,7 @@
         <v>20260526</v>
       </c>
       <c r="K192" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -18763,7 +19046,7 @@
         <v>20260526</v>
       </c>
       <c r="K193" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -18856,7 +19139,7 @@
         <v>20260526</v>
       </c>
       <c r="K194" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -18949,7 +19232,7 @@
         <v>20260526</v>
       </c>
       <c r="K195" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -19042,7 +19325,7 @@
         <v>20260526</v>
       </c>
       <c r="K196" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -19135,7 +19418,7 @@
         <v>20260526</v>
       </c>
       <c r="K197" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -19228,7 +19511,7 @@
         <v>20260526</v>
       </c>
       <c r="K198" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -19321,7 +19604,7 @@
         <v>20260526</v>
       </c>
       <c r="K199" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -19414,7 +19697,7 @@
         <v>20260526</v>
       </c>
       <c r="K200" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -19507,7 +19790,7 @@
         <v>20260526</v>
       </c>
       <c r="K201" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -19600,7 +19883,7 @@
         <v>20260526</v>
       </c>
       <c r="K202" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -19693,7 +19976,7 @@
         <v>20260526</v>
       </c>
       <c r="K203" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -19786,7 +20069,7 @@
         <v>20260526</v>
       </c>
       <c r="K204" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -19879,7 +20162,7 @@
         <v>20260526</v>
       </c>
       <c r="K205" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L205" t="n">
         <v>1800</v>
@@ -19972,7 +20255,7 @@
         <v>20260526</v>
       </c>
       <c r="K206" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -20065,7 +20348,7 @@
         <v>20260526</v>
       </c>
       <c r="K207" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -20158,7 +20441,7 @@
         <v>20260526</v>
       </c>
       <c r="K208" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -20251,7 +20534,7 @@
         <v>20260526</v>
       </c>
       <c r="K209" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -20344,7 +20627,7 @@
         <v>20260526</v>
       </c>
       <c r="K210" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -20437,7 +20720,7 @@
         <v>20260526</v>
       </c>
       <c r="K211" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -20542,7 +20825,7 @@
         <v>20260526</v>
       </c>
       <c r="K212" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -20647,7 +20930,7 @@
         <v>20260526</v>
       </c>
       <c r="K213" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L213" t="n">
         <v>1200</v>
@@ -20752,7 +21035,7 @@
         <v>20260526</v>
       </c>
       <c r="K214" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -20857,7 +21140,7 @@
         <v>20260526</v>
       </c>
       <c r="K215" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L215" t="n">
         <v>3600</v>
@@ -20962,7 +21245,7 @@
         <v>20260526</v>
       </c>
       <c r="K216" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -21055,7 +21338,7 @@
         <v>20260526</v>
       </c>
       <c r="K217" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -21148,7 +21431,7 @@
         <v>20260526</v>
       </c>
       <c r="K218" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -21241,7 +21524,7 @@
         <v>20260526</v>
       </c>
       <c r="K219" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -21334,7 +21617,7 @@
         <v>20260526</v>
       </c>
       <c r="K220" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -21427,7 +21710,7 @@
         <v>20260526</v>
       </c>
       <c r="K221" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>
@@ -21520,7 +21803,7 @@
         <v>20260526</v>
       </c>
       <c r="K222" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
@@ -21613,7 +21896,7 @@
         <v>20260526</v>
       </c>
       <c r="K223" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L223" t="n">
         <v>0</v>
@@ -21706,7 +21989,7 @@
         <v>20260526</v>
       </c>
       <c r="K224" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -21799,7 +22082,7 @@
         <v>20260526</v>
       </c>
       <c r="K225" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L225" t="n">
         <v>0</v>
@@ -21892,7 +22175,7 @@
         <v>20260526</v>
       </c>
       <c r="K226" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -21985,7 +22268,7 @@
         <v>20260526</v>
       </c>
       <c r="K227" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L227" t="n">
         <v>0</v>
@@ -22078,7 +22361,7 @@
         <v>20260526</v>
       </c>
       <c r="K228" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L228" t="n">
         <v>0</v>
@@ -22171,7 +22454,7 @@
         <v>20260526</v>
       </c>
       <c r="K229" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L229" t="n">
         <v>0</v>
@@ -22264,7 +22547,7 @@
         <v>20260526</v>
       </c>
       <c r="K230" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -22357,7 +22640,7 @@
         <v>20260526</v>
       </c>
       <c r="K231" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L231" t="n">
         <v>0</v>
@@ -22450,7 +22733,7 @@
         <v>20260526</v>
       </c>
       <c r="K232" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -22543,7 +22826,7 @@
         <v>20260526</v>
       </c>
       <c r="K233" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L233" t="n">
         <v>300</v>
@@ -22636,7 +22919,7 @@
         <v>20260526</v>
       </c>
       <c r="K234" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L234" t="n">
         <v>300</v>
@@ -22729,7 +23012,7 @@
         <v>20260526</v>
       </c>
       <c r="K235" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -22822,7 +23105,7 @@
         <v>20260526</v>
       </c>
       <c r="K236" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -22915,7 +23198,7 @@
         <v>20260526</v>
       </c>
       <c r="K237" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -23008,7 +23291,7 @@
         <v>20260526</v>
       </c>
       <c r="K238" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -23101,7 +23384,7 @@
         <v>20260526</v>
       </c>
       <c r="K239" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -23194,7 +23477,7 @@
         <v>20260526</v>
       </c>
       <c r="K240" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -23287,7 +23570,7 @@
         <v>20260526</v>
       </c>
       <c r="K241" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -23380,7 +23663,7 @@
         <v>20260526</v>
       </c>
       <c r="K242" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -23473,7 +23756,7 @@
         <v>20260526</v>
       </c>
       <c r="K243" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -23566,7 +23849,7 @@
         <v>20260526</v>
       </c>
       <c r="K244" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -23659,7 +23942,7 @@
         <v>20260526</v>
       </c>
       <c r="K245" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -23752,7 +24035,7 @@
         <v>20260526</v>
       </c>
       <c r="K246" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -23845,7 +24128,7 @@
         <v>20260526</v>
       </c>
       <c r="K247" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L247" t="n">
         <v>300</v>
@@ -23938,7 +24221,7 @@
         <v>20260526</v>
       </c>
       <c r="K248" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -24031,7 +24314,7 @@
         <v>20260526</v>
       </c>
       <c r="K249" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -24124,7 +24407,7 @@
         <v>20260526</v>
       </c>
       <c r="K250" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -24217,7 +24500,7 @@
         <v>20260526</v>
       </c>
       <c r="K251" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L251" t="n">
         <v>0</v>
@@ -24310,7 +24593,7 @@
         <v>20260526</v>
       </c>
       <c r="K252" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -24415,7 +24698,7 @@
         <v>20260526</v>
       </c>
       <c r="K253" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L253" t="n">
         <v>3600</v>
@@ -24520,7 +24803,7 @@
         <v>20260526</v>
       </c>
       <c r="K254" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -24613,7 +24896,7 @@
         <v>20260526</v>
       </c>
       <c r="K255" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -24706,7 +24989,7 @@
         <v>20260526</v>
       </c>
       <c r="K256" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -24799,7 +25082,7 @@
         <v>20260526</v>
       </c>
       <c r="K257" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -24892,7 +25175,7 @@
         <v>20260526</v>
       </c>
       <c r="K258" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L258" t="n">
         <v>0</v>
@@ -24985,7 +25268,7 @@
         <v>20260526</v>
       </c>
       <c r="K259" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -25078,7 +25361,7 @@
         <v>20260526</v>
       </c>
       <c r="K260" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>
@@ -25171,13 +25454,13 @@
         <v>20260526</v>
       </c>
       <c r="K261" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L261" t="n">
         <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="N261" t="inlineStr">
         <is>
@@ -25186,7 +25469,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>16:59:00</t>
+          <t>17:29:00</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -25264,29 +25547,29 @@
         <v>20260526</v>
       </c>
       <c r="K262" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>17:46:00</t>
+          <t>18:16:00</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>17:46:00</t>
+          <t>18:16:00</t>
         </is>
       </c>
       <c r="P262" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="Q262" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R262" t="inlineStr">
         <is>
@@ -25357,7 +25640,7 @@
         <v>20260526</v>
       </c>
       <c r="K263" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -25450,7 +25733,7 @@
         <v>20260526</v>
       </c>
       <c r="K264" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L264" t="n">
         <v>0</v>
@@ -25543,7 +25826,7 @@
         <v>20260526</v>
       </c>
       <c r="K265" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L265" t="n">
         <v>0</v>
@@ -25636,7 +25919,7 @@
         <v>20260526</v>
       </c>
       <c r="K266" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L266" t="n">
         <v>0</v>
@@ -25729,7 +26012,7 @@
         <v>20260526</v>
       </c>
       <c r="K267" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L267" t="n">
         <v>0</v>
@@ -25822,7 +26105,7 @@
         <v>20260526</v>
       </c>
       <c r="K268" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L268" t="n">
         <v>0</v>
@@ -25915,7 +26198,7 @@
         <v>20260526</v>
       </c>
       <c r="K269" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L269" t="n">
         <v>0</v>
@@ -26008,7 +26291,7 @@
         <v>20260526</v>
       </c>
       <c r="K270" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -26101,7 +26384,7 @@
         <v>20260526</v>
       </c>
       <c r="K271" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L271" t="n">
         <v>0</v>
@@ -26194,7 +26477,7 @@
         <v>20260526</v>
       </c>
       <c r="K272" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L272" t="n">
         <v>0</v>
@@ -26287,7 +26570,7 @@
         <v>20260526</v>
       </c>
       <c r="K273" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L273" t="n">
         <v>0</v>
@@ -26380,7 +26663,7 @@
         <v>20260526</v>
       </c>
       <c r="K274" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L274" t="n">
         <v>0</v>
@@ -26473,7 +26756,7 @@
         <v>20260526</v>
       </c>
       <c r="K275" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L275" t="n">
         <v>0</v>
@@ -26566,7 +26849,7 @@
         <v>20260526</v>
       </c>
       <c r="K276" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L276" t="n">
         <v>0</v>
@@ -26659,7 +26942,7 @@
         <v>20260526</v>
       </c>
       <c r="K277" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L277" t="n">
         <v>0</v>
@@ -26752,7 +27035,7 @@
         <v>20260526</v>
       </c>
       <c r="K278" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
@@ -26845,7 +27128,7 @@
         <v>20260526</v>
       </c>
       <c r="K279" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L279" t="n">
         <v>0</v>
@@ -26938,7 +27221,7 @@
         <v>20260526</v>
       </c>
       <c r="K280" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L280" t="n">
         <v>0</v>
@@ -27031,7 +27314,7 @@
         <v>20260526</v>
       </c>
       <c r="K281" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L281" t="n">
         <v>0</v>
@@ -27124,7 +27407,7 @@
         <v>20260526</v>
       </c>
       <c r="K282" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L282" t="n">
         <v>0</v>
@@ -27217,7 +27500,7 @@
         <v>20260526</v>
       </c>
       <c r="K283" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L283" t="n">
         <v>600</v>
@@ -27310,7 +27593,7 @@
         <v>20260526</v>
       </c>
       <c r="K284" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L284" t="n">
         <v>300</v>
@@ -27403,7 +27686,7 @@
         <v>20260526</v>
       </c>
       <c r="K285" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L285" t="n">
         <v>600</v>
@@ -27496,7 +27779,7 @@
         <v>20260526</v>
       </c>
       <c r="K286" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L286" t="n">
         <v>0</v>
@@ -27589,7 +27872,7 @@
         <v>20260526</v>
       </c>
       <c r="K287" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L287" t="n">
         <v>900</v>
@@ -27682,7 +27965,7 @@
         <v>20260526</v>
       </c>
       <c r="K288" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L288" t="n">
         <v>900</v>
@@ -27775,7 +28058,7 @@
         <v>20260526</v>
       </c>
       <c r="K289" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L289" t="n">
         <v>1200</v>
@@ -27868,7 +28151,7 @@
         <v>20260526</v>
       </c>
       <c r="K290" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L290" t="n">
         <v>0</v>
@@ -27973,7 +28256,7 @@
         <v>20260526</v>
       </c>
       <c r="K291" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L291" t="n">
         <v>2400</v>
@@ -28078,7 +28361,7 @@
         <v>20260526</v>
       </c>
       <c r="K292" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L292" t="n">
         <v>2400</v>
@@ -28183,7 +28466,7 @@
         <v>20260526</v>
       </c>
       <c r="K293" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L293" t="n">
         <v>2400</v>
@@ -28288,7 +28571,7 @@
         <v>20260526</v>
       </c>
       <c r="K294" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L294" t="n">
         <v>0</v>
@@ -28381,7 +28664,7 @@
         <v>20260526</v>
       </c>
       <c r="K295" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -28474,7 +28757,7 @@
         <v>20260526</v>
       </c>
       <c r="K296" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L296" t="n">
         <v>0</v>
@@ -28567,7 +28850,7 @@
         <v>20260526</v>
       </c>
       <c r="K297" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L297" t="n">
         <v>0</v>
@@ -28660,7 +28943,7 @@
         <v>20260526</v>
       </c>
       <c r="K298" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L298" t="n">
         <v>0</v>
@@ -28753,7 +29036,7 @@
         <v>20260526</v>
       </c>
       <c r="K299" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L299" t="n">
         <v>0</v>
@@ -28846,7 +29129,7 @@
         <v>20260526</v>
       </c>
       <c r="K300" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L300" t="n">
         <v>0</v>
@@ -28939,7 +29222,7 @@
         <v>20260526</v>
       </c>
       <c r="K301" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L301" t="n">
         <v>0</v>
@@ -29032,7 +29315,7 @@
         <v>20260526</v>
       </c>
       <c r="K302" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L302" t="n">
         <v>0</v>
@@ -29125,7 +29408,7 @@
         <v>20260526</v>
       </c>
       <c r="K303" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L303" t="n">
         <v>0</v>
@@ -29218,7 +29501,7 @@
         <v>20260526</v>
       </c>
       <c r="K304" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L304" t="n">
         <v>0</v>
@@ -29311,7 +29594,7 @@
         <v>20260526</v>
       </c>
       <c r="K305" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L305" t="n">
         <v>0</v>
@@ -29404,7 +29687,7 @@
         <v>20260526</v>
       </c>
       <c r="K306" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L306" t="n">
         <v>0</v>
@@ -29497,7 +29780,7 @@
         <v>20260526</v>
       </c>
       <c r="K307" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L307" t="n">
         <v>0</v>
@@ -29590,7 +29873,7 @@
         <v>20260526</v>
       </c>
       <c r="K308" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L308" t="n">
         <v>0</v>
@@ -29683,7 +29966,7 @@
         <v>20260526</v>
       </c>
       <c r="K309" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L309" t="n">
         <v>0</v>
@@ -29776,7 +30059,7 @@
         <v>20260526</v>
       </c>
       <c r="K310" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L310" t="n">
         <v>0</v>
@@ -29881,7 +30164,7 @@
         <v>20260526</v>
       </c>
       <c r="K311" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L311" t="n">
         <v>300</v>
@@ -29986,7 +30269,7 @@
         <v>20260526</v>
       </c>
       <c r="K312" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L312" t="n">
         <v>300</v>
@@ -30091,7 +30374,7 @@
         <v>20260526</v>
       </c>
       <c r="K313" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L313" t="n">
         <v>4200</v>
@@ -30196,7 +30479,7 @@
         <v>20260526</v>
       </c>
       <c r="K314" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L314" t="n">
         <v>0</v>
@@ -30289,13 +30572,13 @@
         <v>20260526</v>
       </c>
       <c r="K315" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L315" t="n">
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N315" t="inlineStr">
         <is>
@@ -30304,7 +30587,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>16:34:00</t>
+          <t>16:44:00</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -30382,29 +30665,29 @@
         <v>20260526</v>
       </c>
       <c r="K316" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M316" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>16:52:00</t>
+          <t>17:02:00</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>16:57:00</t>
+          <t>17:07:00</t>
         </is>
       </c>
       <c r="P316" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Q316" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R316" t="inlineStr">
         <is>
@@ -30475,29 +30758,29 @@
         <v>20260526</v>
       </c>
       <c r="K317" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M317" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>18:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>18:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="P317" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Q317" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R317" t="inlineStr">
         <is>
@@ -30568,7 +30851,7 @@
         <v>20260526</v>
       </c>
       <c r="K318" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L318" t="n">
         <v>0</v>
@@ -30661,7 +30944,7 @@
         <v>20260526</v>
       </c>
       <c r="K319" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L319" t="n">
         <v>0</v>
@@ -30754,7 +31037,7 @@
         <v>20260526</v>
       </c>
       <c r="K320" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L320" t="n">
         <v>0</v>
@@ -30847,7 +31130,7 @@
         <v>20260526</v>
       </c>
       <c r="K321" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L321" t="n">
         <v>0</v>
@@ -30940,7 +31223,7 @@
         <v>20260526</v>
       </c>
       <c r="K322" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L322" t="n">
         <v>0</v>
@@ -31033,7 +31316,7 @@
         <v>20260526</v>
       </c>
       <c r="K323" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L323" t="n">
         <v>0</v>
@@ -31126,7 +31409,7 @@
         <v>20260526</v>
       </c>
       <c r="K324" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L324" t="n">
         <v>0</v>
@@ -31219,7 +31502,7 @@
         <v>20260526</v>
       </c>
       <c r="K325" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L325" t="n">
         <v>300</v>
@@ -31312,7 +31595,7 @@
         <v>20260526</v>
       </c>
       <c r="K326" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L326" t="n">
         <v>300</v>
@@ -31405,7 +31688,7 @@
         <v>20260526</v>
       </c>
       <c r="K327" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L327" t="n">
         <v>300</v>
@@ -31498,7 +31781,7 @@
         <v>20260526</v>
       </c>
       <c r="K328" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L328" t="n">
         <v>900</v>
@@ -31591,7 +31874,7 @@
         <v>20260526</v>
       </c>
       <c r="K329" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L329" t="n">
         <v>900</v>
@@ -31684,7 +31967,7 @@
         <v>20260526</v>
       </c>
       <c r="K330" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L330" t="n">
         <v>900</v>
@@ -31777,7 +32060,7 @@
         <v>20260526</v>
       </c>
       <c r="K331" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L331" t="n">
         <v>900</v>
@@ -31870,7 +32153,7 @@
         <v>20260526</v>
       </c>
       <c r="K332" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L332" t="n">
         <v>900</v>
@@ -31963,7 +32246,7 @@
         <v>20260526</v>
       </c>
       <c r="K333" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L333" t="n">
         <v>0</v>
@@ -32056,7 +32339,7 @@
         <v>20260526</v>
       </c>
       <c r="K334" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L334" t="n">
         <v>0</v>
@@ -32149,7 +32432,7 @@
         <v>20260526</v>
       </c>
       <c r="K335" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L335" t="n">
         <v>0</v>
@@ -32242,7 +32525,7 @@
         <v>20260526</v>
       </c>
       <c r="K336" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L336" t="n">
         <v>0</v>
@@ -32335,7 +32618,7 @@
         <v>20260526</v>
       </c>
       <c r="K337" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L337" t="n">
         <v>0</v>
@@ -32428,7 +32711,7 @@
         <v>20260526</v>
       </c>
       <c r="K338" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L338" t="n">
         <v>0</v>
@@ -32521,7 +32804,7 @@
         <v>20260526</v>
       </c>
       <c r="K339" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L339" t="n">
         <v>0</v>
@@ -32614,7 +32897,7 @@
         <v>20260526</v>
       </c>
       <c r="K340" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L340" t="n">
         <v>0</v>
@@ -32707,7 +32990,7 @@
         <v>20260526</v>
       </c>
       <c r="K341" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L341" t="n">
         <v>0</v>
@@ -32800,7 +33083,7 @@
         <v>20260526</v>
       </c>
       <c r="K342" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L342" t="n">
         <v>0</v>
@@ -32893,7 +33176,7 @@
         <v>20260526</v>
       </c>
       <c r="K343" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L343" t="n">
         <v>0</v>
@@ -32986,7 +33269,7 @@
         <v>20260526</v>
       </c>
       <c r="K344" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L344" t="n">
         <v>0</v>
@@ -33079,7 +33362,7 @@
         <v>20260526</v>
       </c>
       <c r="K345" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L345" t="n">
         <v>0</v>
@@ -33172,7 +33455,7 @@
         <v>20260526</v>
       </c>
       <c r="K346" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L346" t="n">
         <v>0</v>
@@ -33265,7 +33548,7 @@
         <v>20260526</v>
       </c>
       <c r="K347" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L347" t="n">
         <v>0</v>
@@ -33358,7 +33641,7 @@
         <v>20260526</v>
       </c>
       <c r="K348" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L348" t="n">
         <v>0</v>
@@ -33451,7 +33734,7 @@
         <v>20260526</v>
       </c>
       <c r="K349" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L349" t="n">
         <v>0</v>
@@ -33544,7 +33827,7 @@
         <v>20260526</v>
       </c>
       <c r="K350" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L350" t="n">
         <v>0</v>
@@ -33637,7 +33920,7 @@
         <v>20260526</v>
       </c>
       <c r="K351" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L351" t="n">
         <v>0</v>
@@ -33730,7 +34013,7 @@
         <v>20260526</v>
       </c>
       <c r="K352" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L352" t="n">
         <v>0</v>
@@ -33823,7 +34106,7 @@
         <v>20260526</v>
       </c>
       <c r="K353" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L353" t="n">
         <v>0</v>
@@ -33916,7 +34199,7 @@
         <v>20260526</v>
       </c>
       <c r="K354" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L354" t="n">
         <v>0</v>
@@ -34009,7 +34292,7 @@
         <v>20260526</v>
       </c>
       <c r="K355" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L355" t="n">
         <v>0</v>
@@ -34102,7 +34385,7 @@
         <v>20260526</v>
       </c>
       <c r="K356" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L356" t="n">
         <v>0</v>
@@ -34195,7 +34478,7 @@
         <v>20260526</v>
       </c>
       <c r="K357" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L357" t="n">
         <v>0</v>
@@ -34288,7 +34571,7 @@
         <v>20260526</v>
       </c>
       <c r="K358" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L358" t="n">
         <v>0</v>
@@ -34381,7 +34664,7 @@
         <v>20260526</v>
       </c>
       <c r="K359" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L359" t="n">
         <v>300</v>
@@ -34474,7 +34757,7 @@
         <v>20260526</v>
       </c>
       <c r="K360" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L360" t="n">
         <v>300</v>
@@ -34567,7 +34850,7 @@
         <v>20260526</v>
       </c>
       <c r="K361" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L361" t="n">
         <v>300</v>
@@ -34660,7 +34943,7 @@
         <v>20260526</v>
       </c>
       <c r="K362" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L362" t="n">
         <v>0</v>
@@ -34753,7 +35036,7 @@
         <v>20260526</v>
       </c>
       <c r="K363" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L363" t="n">
         <v>0</v>
@@ -34846,7 +35129,7 @@
         <v>20260526</v>
       </c>
       <c r="K364" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L364" t="n">
         <v>0</v>
@@ -34939,7 +35222,7 @@
         <v>20260526</v>
       </c>
       <c r="K365" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L365" t="n">
         <v>300</v>
@@ -35032,7 +35315,7 @@
         <v>20260526</v>
       </c>
       <c r="K366" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L366" t="n">
         <v>300</v>
@@ -35125,7 +35408,7 @@
         <v>20260526</v>
       </c>
       <c r="K367" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L367" t="n">
         <v>300</v>
@@ -35218,7 +35501,7 @@
         <v>20260526</v>
       </c>
       <c r="K368" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L368" t="n">
         <v>300</v>
@@ -35311,7 +35594,7 @@
         <v>20260526</v>
       </c>
       <c r="K369" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L369" t="n">
         <v>300</v>
@@ -35404,7 +35687,7 @@
         <v>20260526</v>
       </c>
       <c r="K370" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L370" t="n">
         <v>300</v>
@@ -35497,7 +35780,7 @@
         <v>20260526</v>
       </c>
       <c r="K371" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L371" t="n">
         <v>0</v>
@@ -35590,7 +35873,7 @@
         <v>20260526</v>
       </c>
       <c r="K372" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L372" t="n">
         <v>0</v>
@@ -35683,7 +35966,7 @@
         <v>20260526</v>
       </c>
       <c r="K373" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L373" t="n">
         <v>0</v>
@@ -35776,7 +36059,7 @@
         <v>20260526</v>
       </c>
       <c r="K374" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L374" t="n">
         <v>0</v>
@@ -35869,7 +36152,7 @@
         <v>20260526</v>
       </c>
       <c r="K375" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L375" t="n">
         <v>0</v>
@@ -35962,7 +36245,7 @@
         <v>20260526</v>
       </c>
       <c r="K376" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
@@ -36055,7 +36338,7 @@
         <v>20260526</v>
       </c>
       <c r="K377" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L377" t="n">
         <v>0</v>
@@ -36148,7 +36431,7 @@
         <v>20260526</v>
       </c>
       <c r="K378" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L378" t="n">
         <v>0</v>
@@ -36241,7 +36524,7 @@
         <v>20260526</v>
       </c>
       <c r="K379" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L379" t="n">
         <v>0</v>
@@ -36334,7 +36617,7 @@
         <v>20260526</v>
       </c>
       <c r="K380" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L380" t="n">
         <v>0</v>
@@ -36427,7 +36710,7 @@
         <v>20260526</v>
       </c>
       <c r="K381" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L381" t="n">
         <v>0</v>
@@ -36520,7 +36803,7 @@
         <v>20260526</v>
       </c>
       <c r="K382" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L382" t="n">
         <v>0</v>
@@ -36613,7 +36896,7 @@
         <v>20260526</v>
       </c>
       <c r="K383" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L383" t="n">
         <v>0</v>
@@ -36706,7 +36989,7 @@
         <v>20260526</v>
       </c>
       <c r="K384" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L384" t="n">
         <v>0</v>
@@ -36799,7 +37082,7 @@
         <v>20260526</v>
       </c>
       <c r="K385" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L385" t="n">
         <v>0</v>
@@ -36892,7 +37175,7 @@
         <v>20260526</v>
       </c>
       <c r="K386" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L386" t="n">
         <v>0</v>
@@ -36985,7 +37268,7 @@
         <v>20260526</v>
       </c>
       <c r="K387" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L387" t="n">
         <v>900</v>
@@ -37078,7 +37361,7 @@
         <v>20260526</v>
       </c>
       <c r="K388" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L388" t="n">
         <v>1200</v>
@@ -37171,7 +37454,7 @@
         <v>20260526</v>
       </c>
       <c r="K389" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L389" t="n">
         <v>0</v>
@@ -37264,7 +37547,7 @@
         <v>20260526</v>
       </c>
       <c r="K390" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L390" t="n">
         <v>0</v>
@@ -37357,7 +37640,7 @@
         <v>20260526</v>
       </c>
       <c r="K391" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L391" t="n">
         <v>0</v>
@@ -37450,7 +37733,7 @@
         <v>20260526</v>
       </c>
       <c r="K392" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L392" t="n">
         <v>0</v>
@@ -37543,7 +37826,7 @@
         <v>20260526</v>
       </c>
       <c r="K393" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L393" t="n">
         <v>0</v>
@@ -37636,7 +37919,7 @@
         <v>20260526</v>
       </c>
       <c r="K394" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L394" t="n">
         <v>0</v>
@@ -37729,7 +38012,7 @@
         <v>20260526</v>
       </c>
       <c r="K395" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L395" t="n">
         <v>0</v>
@@ -37822,7 +38105,7 @@
         <v>20260526</v>
       </c>
       <c r="K396" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L396" t="n">
         <v>0</v>
@@ -37915,7 +38198,7 @@
         <v>20260526</v>
       </c>
       <c r="K397" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L397" t="n">
         <v>0</v>
@@ -38008,7 +38291,7 @@
         <v>20260526</v>
       </c>
       <c r="K398" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L398" t="n">
         <v>0</v>
@@ -38101,7 +38384,7 @@
         <v>20260526</v>
       </c>
       <c r="K399" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L399" t="n">
         <v>0</v>
@@ -38194,7 +38477,7 @@
         <v>20260526</v>
       </c>
       <c r="K400" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L400" t="n">
         <v>0</v>
@@ -38287,13 +38570,13 @@
         <v>20260526</v>
       </c>
       <c r="K401" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L401" t="n">
         <v>300</v>
       </c>
       <c r="M401" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N401" t="inlineStr">
         <is>
@@ -38302,7 +38585,7 @@
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t>15:14:00</t>
+          <t>15:16:00</t>
         </is>
       </c>
       <c r="P401" t="n">
@@ -38380,13 +38663,13 @@
         <v>20260526</v>
       </c>
       <c r="K402" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L402" t="n">
         <v>300</v>
       </c>
       <c r="M402" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N402" t="inlineStr">
         <is>
@@ -38395,7 +38678,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>16:01:00</t>
+          <t>16:02:00</t>
         </is>
       </c>
       <c r="P402" t="n">
@@ -38473,29 +38756,29 @@
         <v>20260526</v>
       </c>
       <c r="K403" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L403" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M403" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N403" t="inlineStr">
         <is>
-          <t>16:38:00</t>
+          <t>16:48:00</t>
         </is>
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>16:41:00</t>
+          <t>16:51:00</t>
         </is>
       </c>
       <c r="P403" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Q403" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R403" t="inlineStr">
         <is>
@@ -38566,29 +38849,29 @@
         <v>20260526</v>
       </c>
       <c r="K404" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M404" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t>17:40:00</t>
+          <t>17:45:00</t>
         </is>
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>17:50:00</t>
+          <t>17:55:00</t>
         </is>
       </c>
       <c r="P404" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q404" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R404" t="inlineStr">
         <is>
@@ -38659,29 +38942,29 @@
         <v>20260526</v>
       </c>
       <c r="K405" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L405" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M405" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t>18:17:00</t>
+          <t>18:22:00</t>
         </is>
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>18:22:00</t>
+          <t>18:27:00</t>
         </is>
       </c>
       <c r="P405" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q405" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R405" t="inlineStr">
         <is>
@@ -38752,29 +39035,29 @@
         <v>20260526</v>
       </c>
       <c r="K406" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L406" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M406" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t>18:44:00</t>
+          <t>18:49:00</t>
         </is>
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>18:47:00</t>
+          <t>18:52:00</t>
         </is>
       </c>
       <c r="P406" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q406" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R406" t="inlineStr">
         <is>
@@ -38845,29 +39128,29 @@
         <v>20260526</v>
       </c>
       <c r="K407" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M407" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t>19:09:00</t>
+          <t>19:14:00</t>
         </is>
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>19:12:00</t>
+          <t>19:17:00</t>
         </is>
       </c>
       <c r="P407" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q407" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R407" t="inlineStr">
         <is>
@@ -38938,29 +39221,29 @@
         <v>20260526</v>
       </c>
       <c r="K408" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L408" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M408" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t>19:41:00</t>
+          <t>19:46:00</t>
         </is>
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>19:44:00</t>
+          <t>19:49:00</t>
         </is>
       </c>
       <c r="P408" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q408" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R408" t="inlineStr">
         <is>
@@ -39031,29 +39314,29 @@
         <v>20260526</v>
       </c>
       <c r="K409" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L409" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M409" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>20:13:00</t>
+          <t>20:18:00</t>
         </is>
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>20:21:00</t>
+          <t>20:26:00</t>
         </is>
       </c>
       <c r="P409" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q409" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R409" t="inlineStr">
         <is>
@@ -39124,29 +39407,29 @@
         <v>20260526</v>
       </c>
       <c r="K410" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L410" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M410" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t>21:09:00</t>
+          <t>21:14:00</t>
         </is>
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>21:09:00</t>
+          <t>21:14:00</t>
         </is>
       </c>
       <c r="P410" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q410" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R410" t="inlineStr">
         <is>
@@ -39217,7 +39500,7 @@
         <v>20260526</v>
       </c>
       <c r="K411" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L411" t="n">
         <v>0</v>
@@ -39322,7 +39605,7 @@
         <v>20260526</v>
       </c>
       <c r="K412" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L412" t="n">
         <v>0</v>
@@ -39427,7 +39710,7 @@
         <v>20260526</v>
       </c>
       <c r="K413" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L413" t="n">
         <v>0</v>
@@ -39532,7 +39815,7 @@
         <v>20260526</v>
       </c>
       <c r="K414" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L414" t="n">
         <v>0</v>
@@ -39637,7 +39920,7 @@
         <v>20260526</v>
       </c>
       <c r="K415" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L415" t="n">
         <v>0</v>
@@ -39742,7 +40025,7 @@
         <v>20260526</v>
       </c>
       <c r="K416" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L416" t="n">
         <v>0</v>
@@ -39847,7 +40130,7 @@
         <v>20260526</v>
       </c>
       <c r="K417" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L417" t="n">
         <v>0</v>
@@ -39952,7 +40235,7 @@
         <v>20260526</v>
       </c>
       <c r="K418" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L418" t="n">
         <v>0</v>
@@ -40057,7 +40340,7 @@
         <v>20260526</v>
       </c>
       <c r="K419" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L419" t="n">
         <v>300</v>
@@ -40162,7 +40445,7 @@
         <v>20260526</v>
       </c>
       <c r="K420" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L420" t="n">
         <v>300</v>
@@ -40267,7 +40550,7 @@
         <v>20260526</v>
       </c>
       <c r="K421" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L421" t="n">
         <v>300</v>
@@ -40372,7 +40655,7 @@
         <v>20260526</v>
       </c>
       <c r="K422" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L422" t="n">
         <v>300</v>
@@ -40477,7 +40760,7 @@
         <v>20260526</v>
       </c>
       <c r="K423" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L423" t="n">
         <v>0</v>
@@ -40582,7 +40865,7 @@
         <v>20260526</v>
       </c>
       <c r="K424" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L424" t="n">
         <v>0</v>
@@ -40687,7 +40970,7 @@
         <v>20260526</v>
       </c>
       <c r="K425" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L425" t="n">
         <v>0</v>
@@ -40792,13 +41075,13 @@
         <v>20260526</v>
       </c>
       <c r="K426" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L426" t="n">
         <v>0</v>
       </c>
       <c r="M426" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="N426" t="inlineStr">
         <is>
@@ -40807,7 +41090,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>15:37:00</t>
+          <t>16:27:00</t>
         </is>
       </c>
       <c r="P426" t="n">
@@ -40897,29 +41180,29 @@
         <v>20260526</v>
       </c>
       <c r="K427" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L427" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="M427" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t>16:04:00</t>
+          <t>16:54:00</t>
         </is>
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>16:07:00</t>
+          <t>16:57:00</t>
         </is>
       </c>
       <c r="P427" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="Q427" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="R427" t="inlineStr">
         <is>
@@ -41002,29 +41285,29 @@
         <v>20260526</v>
       </c>
       <c r="K428" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L428" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="M428" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t>16:34:00</t>
+          <t>17:24:00</t>
         </is>
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>16:40:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="P428" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="Q428" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="R428" t="inlineStr">
         <is>
@@ -41107,29 +41390,29 @@
         <v>20260526</v>
       </c>
       <c r="K429" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L429" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="M429" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t>17:45:00</t>
+          <t>18:35:00</t>
         </is>
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>17:45:00</t>
+          <t>18:35:00</t>
         </is>
       </c>
       <c r="P429" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="Q429" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="R429" t="inlineStr">
         <is>
@@ -41212,7 +41495,7 @@
         <v>20260526</v>
       </c>
       <c r="K430" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L430" t="n">
         <v>0</v>
@@ -41305,7 +41588,7 @@
         <v>20260526</v>
       </c>
       <c r="K431" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L431" t="n">
         <v>300</v>
@@ -41398,7 +41681,7 @@
         <v>20260526</v>
       </c>
       <c r="K432" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L432" t="n">
         <v>300</v>
@@ -41491,7 +41774,7 @@
         <v>20260526</v>
       </c>
       <c r="K433" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L433" t="n">
         <v>0</v>
@@ -41584,7 +41867,7 @@
         <v>20260526</v>
       </c>
       <c r="K434" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L434" t="n">
         <v>0</v>
@@ -41677,7 +41960,7 @@
         <v>20260526</v>
       </c>
       <c r="K435" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L435" t="n">
         <v>0</v>
@@ -41770,7 +42053,7 @@
         <v>20260526</v>
       </c>
       <c r="K436" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L436" t="n">
         <v>0</v>
@@ -41863,7 +42146,7 @@
         <v>20260526</v>
       </c>
       <c r="K437" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L437" t="n">
         <v>0</v>
@@ -41956,7 +42239,7 @@
         <v>20260526</v>
       </c>
       <c r="K438" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L438" t="n">
         <v>0</v>
@@ -42049,7 +42332,7 @@
         <v>20260526</v>
       </c>
       <c r="K439" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L439" t="n">
         <v>0</v>
@@ -42142,7 +42425,7 @@
         <v>20260526</v>
       </c>
       <c r="K440" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L440" t="n">
         <v>0</v>
@@ -42235,7 +42518,7 @@
         <v>20260526</v>
       </c>
       <c r="K441" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L441" t="n">
         <v>0</v>
@@ -42340,7 +42623,7 @@
         <v>20260526</v>
       </c>
       <c r="K442" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L442" t="n">
         <v>0</v>
@@ -42445,7 +42728,7 @@
         <v>20260526</v>
       </c>
       <c r="K443" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L443" t="n">
         <v>900</v>
@@ -42550,7 +42833,7 @@
         <v>20260526</v>
       </c>
       <c r="K444" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L444" t="n">
         <v>6600</v>
@@ -42655,7 +42938,7 @@
         <v>20260526</v>
       </c>
       <c r="K445" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L445" t="n">
         <v>7800</v>
@@ -42760,7 +43043,7 @@
         <v>20260526</v>
       </c>
       <c r="K446" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L446" t="n">
         <v>7800</v>
@@ -42865,7 +43148,7 @@
         <v>20260526</v>
       </c>
       <c r="K447" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L447" t="n">
         <v>7800</v>
@@ -42970,7 +43253,7 @@
         <v>20260526</v>
       </c>
       <c r="K448" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L448" t="n">
         <v>7800</v>
@@ -43075,7 +43358,7 @@
         <v>20260526</v>
       </c>
       <c r="K449" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L449" t="n">
         <v>7800</v>
@@ -43180,7 +43463,7 @@
         <v>20260526</v>
       </c>
       <c r="K450" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L450" t="n">
         <v>7800</v>
@@ -43285,7 +43568,7 @@
         <v>20260526</v>
       </c>
       <c r="K451" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L451" t="n">
         <v>7800</v>
@@ -43390,7 +43673,7 @@
         <v>20260526</v>
       </c>
       <c r="K452" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L452" t="n">
         <v>7800</v>
@@ -43495,7 +43778,7 @@
         <v>20260526</v>
       </c>
       <c r="K453" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L453" t="n">
         <v>7800</v>
@@ -43600,7 +43883,7 @@
         <v>20260526</v>
       </c>
       <c r="K454" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L454" t="n">
         <v>7800</v>
@@ -43705,7 +43988,7 @@
         <v>20260526</v>
       </c>
       <c r="K455" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L455" t="n">
         <v>7800</v>
@@ -43810,7 +44093,7 @@
         <v>20260526</v>
       </c>
       <c r="K456" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L456" t="n">
         <v>7800</v>
@@ -43915,7 +44198,7 @@
         <v>20260526</v>
       </c>
       <c r="K457" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L457" t="n">
         <v>7800</v>
@@ -44020,7 +44303,7 @@
         <v>20260526</v>
       </c>
       <c r="K458" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L458" t="n">
         <v>7800</v>
@@ -44125,7 +44408,7 @@
         <v>20260526</v>
       </c>
       <c r="K459" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L459" t="n">
         <v>0</v>
@@ -44218,7 +44501,7 @@
         <v>20260526</v>
       </c>
       <c r="K460" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L460" t="n">
         <v>0</v>
@@ -44311,7 +44594,7 @@
         <v>20260526</v>
       </c>
       <c r="K461" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L461" t="n">
         <v>0</v>
@@ -44416,7 +44699,7 @@
         <v>20260526</v>
       </c>
       <c r="K462" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L462" t="n">
         <v>0</v>
@@ -44521,17 +44804,17 @@
         <v>20260526</v>
       </c>
       <c r="K463" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L463" t="n">
-        <v>7200</v>
+        <v>9000</v>
       </c>
       <c r="M463" t="n">
         <v>1800</v>
       </c>
       <c r="N463" t="inlineStr">
         <is>
-          <t>17:17:00</t>
+          <t>17:47:00</t>
         </is>
       </c>
       <c r="O463" t="inlineStr">
@@ -44540,10 +44823,10 @@
         </is>
       </c>
       <c r="P463" t="n">
-        <v>7200</v>
+        <v>9000</v>
       </c>
       <c r="Q463" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="R463" t="inlineStr">
         <is>
@@ -44626,13 +44909,13 @@
         <v>20260526</v>
       </c>
       <c r="K464" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L464" t="n">
         <v>0</v>
       </c>
       <c r="M464" t="n">
-        <v>3000</v>
+        <v>6600</v>
       </c>
       <c r="N464" t="inlineStr">
         <is>
@@ -44641,7 +44924,7 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>17:06:00</t>
+          <t>18:06:00</t>
         </is>
       </c>
       <c r="P464" t="n">
@@ -44719,7 +45002,7 @@
         <v>20260526</v>
       </c>
       <c r="K465" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L465" t="n">
         <v>3000</v>
@@ -44752,11 +45035,11 @@
         <v>0</v>
       </c>
       <c r="T465" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U465" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="V465" t="inlineStr">
@@ -44812,7 +45095,7 @@
         <v>20260526</v>
       </c>
       <c r="K466" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L466" t="n">
         <v>3000</v>
@@ -44905,7 +45188,7 @@
         <v>20260526</v>
       </c>
       <c r="K467" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L467" t="n">
         <v>0</v>
@@ -44998,7 +45281,7 @@
         <v>20260526</v>
       </c>
       <c r="K468" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L468" t="n">
         <v>0</v>
@@ -45091,7 +45374,7 @@
         <v>20260526</v>
       </c>
       <c r="K469" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L469" t="n">
         <v>0</v>
@@ -45184,7 +45467,7 @@
         <v>20260526</v>
       </c>
       <c r="K470" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L470" t="n">
         <v>0</v>
@@ -45289,7 +45572,7 @@
         <v>20260526</v>
       </c>
       <c r="K471" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L471" t="n">
         <v>0</v>
@@ -45394,7 +45677,7 @@
         <v>20260526</v>
       </c>
       <c r="K472" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L472" t="n">
         <v>0</v>
@@ -45499,7 +45782,7 @@
         <v>20260526</v>
       </c>
       <c r="K473" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L473" t="n">
         <v>0</v>
@@ -45604,7 +45887,7 @@
         <v>20260526</v>
       </c>
       <c r="K474" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L474" t="n">
         <v>0</v>
@@ -45709,7 +45992,7 @@
         <v>20260526</v>
       </c>
       <c r="K475" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L475" t="n">
         <v>0</v>
@@ -45814,7 +46097,7 @@
         <v>20260526</v>
       </c>
       <c r="K476" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L476" t="n">
         <v>0</v>
@@ -45919,29 +46202,29 @@
         <v>20260526</v>
       </c>
       <c r="K477" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L477" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M477" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N477" t="inlineStr">
         <is>
-          <t>19:39:00</t>
+          <t>19:49:00</t>
         </is>
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t>19:40:00</t>
+          <t>19:50:00</t>
         </is>
       </c>
       <c r="P477" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="Q477" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R477" t="inlineStr">
         <is>
@@ -46024,29 +46307,29 @@
         <v>20260526</v>
       </c>
       <c r="K478" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L478" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M478" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N478" t="inlineStr">
         <is>
-          <t>19:51:00</t>
+          <t>19:56:00</t>
         </is>
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t>19:52:00</t>
+          <t>19:57:00</t>
         </is>
       </c>
       <c r="P478" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q478" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R478" t="inlineStr">
         <is>
@@ -46129,29 +46412,29 @@
         <v>20260526</v>
       </c>
       <c r="K479" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L479" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M479" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N479" t="inlineStr">
         <is>
-          <t>19:59:00</t>
+          <t>20:04:00</t>
         </is>
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:05:00</t>
         </is>
       </c>
       <c r="P479" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q479" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R479" t="inlineStr">
         <is>
@@ -46234,13 +46517,13 @@
         <v>20260526</v>
       </c>
       <c r="K480" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L480" t="n">
         <v>0</v>
       </c>
       <c r="M480" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N480" t="inlineStr">
         <is>
@@ -46249,7 +46532,7 @@
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t>20:26:00</t>
+          <t>20:31:00</t>
         </is>
       </c>
       <c r="P480" t="n">
@@ -46339,7 +46622,7 @@
         <v>20260526</v>
       </c>
       <c r="K481" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L481" t="n">
         <v>0</v>
@@ -46432,7 +46715,7 @@
         <v>20260526</v>
       </c>
       <c r="K482" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L482" t="n">
         <v>300</v>
@@ -46525,7 +46808,7 @@
         <v>20260526</v>
       </c>
       <c r="K483" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L483" t="n">
         <v>3000</v>
@@ -46618,7 +46901,7 @@
         <v>20260526</v>
       </c>
       <c r="K484" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L484" t="n">
         <v>3000</v>
@@ -46711,7 +46994,7 @@
         <v>20260526</v>
       </c>
       <c r="K485" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L485" t="n">
         <v>3000</v>
@@ -46804,7 +47087,7 @@
         <v>20260526</v>
       </c>
       <c r="K486" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L486" t="n">
         <v>3000</v>
@@ -46897,7 +47180,7 @@
         <v>20260526</v>
       </c>
       <c r="K487" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L487" t="n">
         <v>0</v>
@@ -47002,7 +47285,7 @@
         <v>20260526</v>
       </c>
       <c r="K488" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L488" t="n">
         <v>300</v>
@@ -47107,7 +47390,7 @@
         <v>20260526</v>
       </c>
       <c r="K489" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L489" t="n">
         <v>300</v>
@@ -47212,7 +47495,7 @@
         <v>20260526</v>
       </c>
       <c r="K490" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L490" t="n">
         <v>300</v>
@@ -47317,7 +47600,7 @@
         <v>20260526</v>
       </c>
       <c r="K491" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L491" t="n">
         <v>3600</v>
@@ -47422,7 +47705,7 @@
         <v>20260526</v>
       </c>
       <c r="K492" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L492" t="n">
         <v>0</v>
@@ -47515,7 +47798,7 @@
         <v>20260526</v>
       </c>
       <c r="K493" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L493" t="n">
         <v>0</v>
@@ -47608,7 +47891,7 @@
         <v>20260526</v>
       </c>
       <c r="K494" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L494" t="n">
         <v>600</v>
@@ -47701,7 +47984,7 @@
         <v>20260526</v>
       </c>
       <c r="K495" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L495" t="n">
         <v>600</v>
@@ -47794,7 +48077,7 @@
         <v>20260526</v>
       </c>
       <c r="K496" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L496" t="n">
         <v>300</v>
@@ -47887,7 +48170,7 @@
         <v>20260526</v>
       </c>
       <c r="K497" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L497" t="n">
         <v>0</v>
@@ -47980,7 +48263,7 @@
         <v>20260526</v>
       </c>
       <c r="K498" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L498" t="n">
         <v>0</v>
@@ -48073,7 +48356,7 @@
         <v>20260526</v>
       </c>
       <c r="K499" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L499" t="n">
         <v>0</v>
@@ -48166,7 +48449,7 @@
         <v>20260526</v>
       </c>
       <c r="K500" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L500" t="n">
         <v>0</v>
@@ -48259,7 +48542,7 @@
         <v>20260526</v>
       </c>
       <c r="K501" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L501" t="n">
         <v>0</v>
@@ -48352,7 +48635,7 @@
         <v>20260526</v>
       </c>
       <c r="K502" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L502" t="n">
         <v>0</v>
@@ -48457,7 +48740,7 @@
         <v>20260526</v>
       </c>
       <c r="K503" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L503" t="n">
         <v>600</v>
@@ -48562,7 +48845,7 @@
         <v>20260526</v>
       </c>
       <c r="K504" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L504" t="n">
         <v>600</v>
@@ -48667,7 +48950,7 @@
         <v>20260526</v>
       </c>
       <c r="K505" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L505" t="n">
         <v>300</v>
@@ -48772,7 +49055,7 @@
         <v>20260526</v>
       </c>
       <c r="K506" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L506" t="n">
         <v>1200</v>
@@ -48877,7 +49160,7 @@
         <v>20260526</v>
       </c>
       <c r="K507" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L507" t="n">
         <v>0</v>
@@ -48970,7 +49253,7 @@
         <v>20260526</v>
       </c>
       <c r="K508" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L508" t="n">
         <v>0</v>
@@ -49063,7 +49346,7 @@
         <v>20260526</v>
       </c>
       <c r="K509" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L509" t="n">
         <v>0</v>
@@ -49156,7 +49439,7 @@
         <v>20260526</v>
       </c>
       <c r="K510" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L510" t="n">
         <v>0</v>
@@ -49249,7 +49532,7 @@
         <v>20260526</v>
       </c>
       <c r="K511" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L511" t="n">
         <v>0</v>
@@ -49342,7 +49625,7 @@
         <v>20260526</v>
       </c>
       <c r="K512" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L512" t="n">
         <v>0</v>
@@ -49435,7 +49718,7 @@
         <v>20260526</v>
       </c>
       <c r="K513" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L513" t="n">
         <v>0</v>
@@ -49528,7 +49811,7 @@
         <v>20260526</v>
       </c>
       <c r="K514" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L514" t="n">
         <v>0</v>
@@ -49621,7 +49904,7 @@
         <v>20260526</v>
       </c>
       <c r="K515" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L515" t="n">
         <v>0</v>
@@ -49714,7 +49997,7 @@
         <v>20260526</v>
       </c>
       <c r="K516" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L516" t="n">
         <v>0</v>
@@ -49807,7 +50090,7 @@
         <v>20260526</v>
       </c>
       <c r="K517" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L517" t="n">
         <v>300</v>
@@ -49900,7 +50183,7 @@
         <v>20260526</v>
       </c>
       <c r="K518" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L518" t="n">
         <v>300</v>
@@ -49993,7 +50276,7 @@
         <v>20260526</v>
       </c>
       <c r="K519" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L519" t="n">
         <v>0</v>
@@ -50098,7 +50381,7 @@
         <v>20260526</v>
       </c>
       <c r="K520" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L520" t="n">
         <v>0</v>
@@ -50203,7 +50486,7 @@
         <v>20260526</v>
       </c>
       <c r="K521" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L521" t="n">
         <v>0</v>
@@ -50308,7 +50591,7 @@
         <v>20260526</v>
       </c>
       <c r="K522" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L522" t="n">
         <v>0</v>
@@ -50413,7 +50696,7 @@
         <v>20260526</v>
       </c>
       <c r="K523" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L523" t="n">
         <v>0</v>
@@ -50518,7 +50801,7 @@
         <v>20260526</v>
       </c>
       <c r="K524" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L524" t="n">
         <v>0</v>
@@ -50623,7 +50906,7 @@
         <v>20260526</v>
       </c>
       <c r="K525" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L525" t="n">
         <v>1800</v>
@@ -50728,7 +51011,7 @@
         <v>20260526</v>
       </c>
       <c r="K526" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L526" t="n">
         <v>3600</v>
@@ -50833,7 +51116,7 @@
         <v>20260526</v>
       </c>
       <c r="K527" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L527" t="n">
         <v>3600</v>
@@ -50938,7 +51221,7 @@
         <v>20260526</v>
       </c>
       <c r="K528" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L528" t="n">
         <v>3600</v>
@@ -51043,7 +51326,7 @@
         <v>20260526</v>
       </c>
       <c r="K529" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L529" t="n">
         <v>0</v>
@@ -51148,7 +51431,7 @@
         <v>20260526</v>
       </c>
       <c r="K530" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L530" t="n">
         <v>3600</v>
@@ -51253,7 +51536,7 @@
         <v>20260526</v>
       </c>
       <c r="K531" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L531" t="n">
         <v>4200</v>
@@ -51358,7 +51641,7 @@
         <v>20260526</v>
       </c>
       <c r="K532" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L532" t="n">
         <v>4200</v>
@@ -51463,7 +51746,7 @@
         <v>20260526</v>
       </c>
       <c r="K533" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L533" t="n">
         <v>3600</v>
@@ -51568,7 +51851,7 @@
         <v>20260526</v>
       </c>
       <c r="K534" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L534" t="n">
         <v>0</v>
@@ -51661,7 +51944,7 @@
         <v>20260526</v>
       </c>
       <c r="K535" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L535" t="n">
         <v>0</v>
@@ -51754,7 +52037,7 @@
         <v>20260526</v>
       </c>
       <c r="K536" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L536" t="n">
         <v>0</v>
@@ -51847,7 +52130,7 @@
         <v>20260526</v>
       </c>
       <c r="K537" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L537" t="n">
         <v>0</v>
@@ -51940,7 +52223,7 @@
         <v>20260526</v>
       </c>
       <c r="K538" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L538" t="n">
         <v>0</v>
@@ -52033,7 +52316,7 @@
         <v>20260526</v>
       </c>
       <c r="K539" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L539" t="n">
         <v>0</v>
@@ -52126,7 +52409,7 @@
         <v>20260526</v>
       </c>
       <c r="K540" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L540" t="n">
         <v>0</v>
@@ -52219,7 +52502,7 @@
         <v>20260526</v>
       </c>
       <c r="K541" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L541" t="n">
         <v>0</v>
@@ -52312,7 +52595,7 @@
         <v>20260526</v>
       </c>
       <c r="K542" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L542" t="n">
         <v>0</v>
@@ -52405,7 +52688,7 @@
         <v>20260526</v>
       </c>
       <c r="K543" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L543" t="n">
         <v>0</v>
@@ -52510,7 +52793,7 @@
         <v>20260526</v>
       </c>
       <c r="K544" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L544" t="n">
         <v>0</v>
@@ -52615,7 +52898,7 @@
         <v>20260526</v>
       </c>
       <c r="K545" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L545" t="n">
         <v>1200</v>
@@ -52720,7 +53003,7 @@
         <v>20260526</v>
       </c>
       <c r="K546" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L546" t="n">
         <v>1200</v>
@@ -52825,7 +53108,7 @@
         <v>20260526</v>
       </c>
       <c r="K547" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L547" t="n">
         <v>0</v>
@@ -52930,7 +53213,7 @@
         <v>20260526</v>
       </c>
       <c r="K548" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L548" t="n">
         <v>0</v>
@@ -53035,7 +53318,7 @@
         <v>20260526</v>
       </c>
       <c r="K549" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L549" t="n">
         <v>0</v>
@@ -53140,7 +53423,7 @@
         <v>20260526</v>
       </c>
       <c r="K550" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L550" t="n">
         <v>0</v>
@@ -53245,7 +53528,7 @@
         <v>20260526</v>
       </c>
       <c r="K551" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L551" t="n">
         <v>0</v>
@@ -53350,7 +53633,7 @@
         <v>20260526</v>
       </c>
       <c r="K552" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L552" t="n">
         <v>0</v>
@@ -53455,7 +53738,7 @@
         <v>20260526</v>
       </c>
       <c r="K553" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L553" t="n">
         <v>0</v>
@@ -53548,7 +53831,7 @@
         <v>20260526</v>
       </c>
       <c r="K554" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L554" t="n">
         <v>600</v>
@@ -53641,7 +53924,7 @@
         <v>20260526</v>
       </c>
       <c r="K555" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L555" t="n">
         <v>600</v>
@@ -53734,7 +54017,7 @@
         <v>20260526</v>
       </c>
       <c r="K556" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L556" t="n">
         <v>900</v>
@@ -53827,7 +54110,7 @@
         <v>20260526</v>
       </c>
       <c r="K557" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L557" t="n">
         <v>0</v>
@@ -53932,7 +54215,7 @@
         <v>20260526</v>
       </c>
       <c r="K558" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L558" t="n">
         <v>0</v>
@@ -54037,7 +54320,7 @@
         <v>20260526</v>
       </c>
       <c r="K559" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L559" t="n">
         <v>600</v>
@@ -54142,7 +54425,7 @@
         <v>20260526</v>
       </c>
       <c r="K560" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L560" t="n">
         <v>0</v>
@@ -54247,7 +54530,7 @@
         <v>20260526</v>
       </c>
       <c r="K561" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L561" t="n">
         <v>0</v>
@@ -54340,7 +54623,7 @@
         <v>20260526</v>
       </c>
       <c r="K562" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L562" t="n">
         <v>300</v>
@@ -54433,7 +54716,7 @@
         <v>20260526</v>
       </c>
       <c r="K563" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L563" t="n">
         <v>600</v>
@@ -54526,7 +54809,7 @@
         <v>20260526</v>
       </c>
       <c r="K564" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L564" t="n">
         <v>600</v>
@@ -54619,7 +54902,7 @@
         <v>20260526</v>
       </c>
       <c r="K565" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L565" t="n">
         <v>600</v>
@@ -54712,7 +54995,7 @@
         <v>20260526</v>
       </c>
       <c r="K566" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L566" t="n">
         <v>600</v>
@@ -54805,7 +55088,7 @@
         <v>20260526</v>
       </c>
       <c r="K567" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L567" t="n">
         <v>600</v>
@@ -54898,13 +55181,13 @@
         <v>20260526</v>
       </c>
       <c r="K568" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L568" t="n">
         <v>0</v>
       </c>
       <c r="M568" t="n">
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="N568" t="inlineStr">
         <is>
@@ -54913,7 +55196,7 @@
       </c>
       <c r="O568" t="inlineStr">
         <is>
-          <t>16:25:00</t>
+          <t>16:55:00</t>
         </is>
       </c>
       <c r="P568" t="n">
@@ -55003,7 +55286,7 @@
         <v>20260526</v>
       </c>
       <c r="K569" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L569" t="n">
         <v>3000</v>
@@ -55108,7 +55391,7 @@
         <v>20260526</v>
       </c>
       <c r="K570" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L570" t="n">
         <v>3600</v>
@@ -55213,7 +55496,7 @@
         <v>20260526</v>
       </c>
       <c r="K571" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L571" t="n">
         <v>3600</v>
@@ -55318,7 +55601,7 @@
         <v>20260526</v>
       </c>
       <c r="K572" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L572" t="n">
         <v>3600</v>
@@ -55423,7 +55706,7 @@
         <v>20260526</v>
       </c>
       <c r="K573" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L573" t="n">
         <v>3300</v>
@@ -55528,7 +55811,7 @@
         <v>20260526</v>
       </c>
       <c r="K574" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L574" t="n">
         <v>3000</v>
@@ -55633,7 +55916,7 @@
         <v>20260526</v>
       </c>
       <c r="K575" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L575" t="n">
         <v>0</v>
@@ -55726,7 +56009,7 @@
         <v>20260526</v>
       </c>
       <c r="K576" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L576" t="n">
         <v>0</v>
@@ -55819,7 +56102,7 @@
         <v>20260526</v>
       </c>
       <c r="K577" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L577" t="n">
         <v>300</v>
@@ -55912,7 +56195,7 @@
         <v>20260526</v>
       </c>
       <c r="K578" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L578" t="n">
         <v>300</v>
@@ -56005,7 +56288,7 @@
         <v>20260526</v>
       </c>
       <c r="K579" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L579" t="n">
         <v>0</v>
@@ -56110,7 +56393,7 @@
         <v>20260526</v>
       </c>
       <c r="K580" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L580" t="n">
         <v>0</v>
@@ -56215,7 +56498,7 @@
         <v>20260526</v>
       </c>
       <c r="K581" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L581" t="n">
         <v>0</v>
@@ -56320,7 +56603,7 @@
         <v>20260526</v>
       </c>
       <c r="K582" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L582" t="n">
         <v>0</v>
@@ -56425,7 +56708,7 @@
         <v>20260526</v>
       </c>
       <c r="K583" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L583" t="n">
         <v>0</v>
@@ -56530,7 +56813,7 @@
         <v>20260526</v>
       </c>
       <c r="K584" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L584" t="n">
         <v>2400</v>
@@ -56635,7 +56918,7 @@
         <v>20260526</v>
       </c>
       <c r="K585" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L585" t="n">
         <v>2400</v>
@@ -56740,7 +57023,7 @@
         <v>20260526</v>
       </c>
       <c r="K586" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L586" t="n">
         <v>1800</v>
@@ -56845,7 +57128,7 @@
         <v>20260526</v>
       </c>
       <c r="K587" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L587" t="n">
         <v>1800</v>
@@ -56950,7 +57233,7 @@
         <v>20260526</v>
       </c>
       <c r="K588" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L588" t="n">
         <v>1800</v>
@@ -57055,7 +57338,7 @@
         <v>20260526</v>
       </c>
       <c r="K589" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L589" t="n">
         <v>1800</v>
@@ -57160,7 +57443,7 @@
         <v>20260526</v>
       </c>
       <c r="K590" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L590" t="n">
         <v>1800</v>
@@ -57265,7 +57548,7 @@
         <v>20260526</v>
       </c>
       <c r="K591" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L591" t="n">
         <v>1800</v>
@@ -57370,7 +57653,7 @@
         <v>20260526</v>
       </c>
       <c r="K592" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L592" t="n">
         <v>1800</v>
@@ -57475,7 +57758,7 @@
         <v>20260526</v>
       </c>
       <c r="K593" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L593" t="n">
         <v>1800</v>
@@ -57580,7 +57863,7 @@
         <v>20260526</v>
       </c>
       <c r="K594" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L594" t="n">
         <v>1800</v>
@@ -57685,7 +57968,7 @@
         <v>20260526</v>
       </c>
       <c r="K595" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L595" t="n">
         <v>1800</v>
@@ -57790,7 +58073,7 @@
         <v>20260526</v>
       </c>
       <c r="K596" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L596" t="n">
         <v>0</v>
@@ -57895,7 +58178,7 @@
         <v>20260526</v>
       </c>
       <c r="K597" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L597" t="n">
         <v>7800</v>
@@ -58000,7 +58283,7 @@
         <v>20260526</v>
       </c>
       <c r="K598" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L598" t="n">
         <v>7800</v>
@@ -58105,7 +58388,7 @@
         <v>20260526</v>
       </c>
       <c r="K599" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L599" t="n">
         <v>7800</v>
@@ -58210,7 +58493,7 @@
         <v>20260526</v>
       </c>
       <c r="K600" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L600" t="n">
         <v>7200</v>
@@ -58315,7 +58598,7 @@
         <v>20260526</v>
       </c>
       <c r="K601" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L601" t="n">
         <v>7200</v>
@@ -58420,7 +58703,7 @@
         <v>20260526</v>
       </c>
       <c r="K602" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L602" t="n">
         <v>7800</v>
@@ -58525,7 +58808,7 @@
         <v>20260526</v>
       </c>
       <c r="K603" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L603" t="n">
         <v>7800</v>
@@ -58630,7 +58913,7 @@
         <v>20260526</v>
       </c>
       <c r="K604" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L604" t="n">
         <v>7800</v>
@@ -58735,7 +59018,7 @@
         <v>20260526</v>
       </c>
       <c r="K605" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L605" t="n">
         <v>8400</v>
@@ -58840,7 +59123,7 @@
         <v>20260526</v>
       </c>
       <c r="K606" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L606" t="n">
         <v>8400</v>
@@ -58945,7 +59228,7 @@
         <v>20260526</v>
       </c>
       <c r="K607" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L607" t="n">
         <v>8400</v>
@@ -59050,7 +59333,7 @@
         <v>20260526</v>
       </c>
       <c r="K608" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L608" t="n">
         <v>8400</v>
@@ -59155,7 +59438,7 @@
         <v>20260526</v>
       </c>
       <c r="K609" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L609" t="n">
         <v>0</v>
@@ -59248,7 +59531,7 @@
         <v>20260526</v>
       </c>
       <c r="K610" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L610" t="n">
         <v>0</v>
@@ -59341,7 +59624,7 @@
         <v>20260526</v>
       </c>
       <c r="K611" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L611" t="n">
         <v>0</v>
@@ -59434,7 +59717,7 @@
         <v>20260526</v>
       </c>
       <c r="K612" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L612" t="n">
         <v>0</v>
@@ -59527,7 +59810,7 @@
         <v>20260526</v>
       </c>
       <c r="K613" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L613" t="n">
         <v>0</v>
@@ -59620,7 +59903,7 @@
         <v>20260526</v>
       </c>
       <c r="K614" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L614" t="n">
         <v>0</v>
@@ -59713,7 +59996,7 @@
         <v>20260526</v>
       </c>
       <c r="K615" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L615" t="n">
         <v>300</v>
@@ -59806,7 +60089,7 @@
         <v>20260526</v>
       </c>
       <c r="K616" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L616" t="n">
         <v>600</v>
@@ -59899,7 +60182,7 @@
         <v>20260526</v>
       </c>
       <c r="K617" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L617" t="n">
         <v>0</v>
@@ -59992,7 +60275,7 @@
         <v>20260526</v>
       </c>
       <c r="K618" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L618" t="n">
         <v>0</v>
@@ -60085,7 +60368,7 @@
         <v>20260526</v>
       </c>
       <c r="K619" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L619" t="n">
         <v>0</v>
@@ -60190,7 +60473,7 @@
         <v>20260526</v>
       </c>
       <c r="K620" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L620" t="n">
         <v>0</v>
@@ -60295,7 +60578,7 @@
         <v>20260526</v>
       </c>
       <c r="K621" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L621" t="n">
         <v>900</v>
@@ -60400,7 +60683,7 @@
         <v>20260526</v>
       </c>
       <c r="K622" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L622" t="n">
         <v>900</v>
@@ -60505,7 +60788,7 @@
         <v>20260526</v>
       </c>
       <c r="K623" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L623" t="n">
         <v>900</v>
@@ -60610,7 +60893,7 @@
         <v>20260526</v>
       </c>
       <c r="K624" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L624" t="n">
         <v>600</v>
@@ -60715,7 +60998,7 @@
         <v>20260526</v>
       </c>
       <c r="K625" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L625" t="n">
         <v>600</v>
@@ -60820,7 +61103,7 @@
         <v>20260526</v>
       </c>
       <c r="K626" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L626" t="n">
         <v>600</v>
@@ -60925,7 +61208,7 @@
         <v>20260526</v>
       </c>
       <c r="K627" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L627" t="n">
         <v>600</v>
@@ -61030,7 +61313,7 @@
         <v>20260526</v>
       </c>
       <c r="K628" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L628" t="n">
         <v>600</v>
@@ -61135,7 +61418,7 @@
         <v>20260526</v>
       </c>
       <c r="K629" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L629" t="n">
         <v>0</v>
@@ -61228,7 +61511,7 @@
         <v>20260526</v>
       </c>
       <c r="K630" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L630" t="n">
         <v>0</v>
@@ -61321,7 +61604,7 @@
         <v>20260526</v>
       </c>
       <c r="K631" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L631" t="n">
         <v>0</v>
@@ -61414,7 +61697,7 @@
         <v>20260526</v>
       </c>
       <c r="K632" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L632" t="n">
         <v>0</v>
@@ -61507,7 +61790,7 @@
         <v>20260526</v>
       </c>
       <c r="K633" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L633" t="n">
         <v>0</v>
@@ -61600,7 +61883,7 @@
         <v>20260526</v>
       </c>
       <c r="K634" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L634" t="n">
         <v>0</v>
@@ -61693,7 +61976,7 @@
         <v>20260526</v>
       </c>
       <c r="K635" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L635" t="n">
         <v>0</v>
@@ -61786,7 +62069,7 @@
         <v>20260526</v>
       </c>
       <c r="K636" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L636" t="n">
         <v>0</v>
@@ -61879,7 +62162,7 @@
         <v>20260526</v>
       </c>
       <c r="K637" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L637" t="n">
         <v>600</v>
@@ -61972,7 +62255,7 @@
         <v>20260526</v>
       </c>
       <c r="K638" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L638" t="n">
         <v>300</v>
@@ -62065,7 +62348,7 @@
         <v>20260526</v>
       </c>
       <c r="K639" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L639" t="n">
         <v>0</v>
@@ -62158,7 +62441,7 @@
         <v>20260526</v>
       </c>
       <c r="K640" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L640" t="n">
         <v>0</v>
@@ -62251,7 +62534,7 @@
         <v>20260526</v>
       </c>
       <c r="K641" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L641" t="n">
         <v>0</v>
@@ -62344,7 +62627,7 @@
         <v>20260526</v>
       </c>
       <c r="K642" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L642" t="n">
         <v>0</v>
@@ -62437,7 +62720,7 @@
         <v>20260526</v>
       </c>
       <c r="K643" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L643" t="n">
         <v>0</v>
@@ -62530,7 +62813,7 @@
         <v>20260526</v>
       </c>
       <c r="K644" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L644" t="n">
         <v>0</v>
@@ -62623,7 +62906,7 @@
         <v>20260526</v>
       </c>
       <c r="K645" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L645" t="n">
         <v>300</v>
@@ -62716,7 +62999,7 @@
         <v>20260526</v>
       </c>
       <c r="K646" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L646" t="n">
         <v>0</v>
@@ -62809,7 +63092,7 @@
         <v>20260526</v>
       </c>
       <c r="K647" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L647" t="n">
         <v>0</v>
@@ -62902,7 +63185,7 @@
         <v>20260526</v>
       </c>
       <c r="K648" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L648" t="n">
         <v>0</v>
@@ -62995,7 +63278,7 @@
         <v>20260526</v>
       </c>
       <c r="K649" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L649" t="n">
         <v>0</v>
@@ -63088,7 +63371,7 @@
         <v>20260526</v>
       </c>
       <c r="K650" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L650" t="n">
         <v>0</v>
@@ -63181,7 +63464,7 @@
         <v>20260526</v>
       </c>
       <c r="K651" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L651" t="n">
         <v>0</v>
@@ -63274,7 +63557,7 @@
         <v>20260526</v>
       </c>
       <c r="K652" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L652" t="n">
         <v>0</v>
@@ -63367,7 +63650,7 @@
         <v>20260526</v>
       </c>
       <c r="K653" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L653" t="n">
         <v>0</v>
@@ -63460,7 +63743,7 @@
         <v>20260526</v>
       </c>
       <c r="K654" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L654" t="n">
         <v>0</v>
@@ -63553,7 +63836,7 @@
         <v>20260526</v>
       </c>
       <c r="K655" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L655" t="n">
         <v>0</v>
@@ -63646,7 +63929,7 @@
         <v>20260526</v>
       </c>
       <c r="K656" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L656" t="n">
         <v>0</v>
@@ -63739,7 +64022,7 @@
         <v>20260526</v>
       </c>
       <c r="K657" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L657" t="n">
         <v>0</v>
@@ -63832,7 +64115,7 @@
         <v>20260526</v>
       </c>
       <c r="K658" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L658" t="n">
         <v>0</v>
@@ -63925,7 +64208,7 @@
         <v>20260526</v>
       </c>
       <c r="K659" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L659" t="n">
         <v>0</v>
@@ -64018,7 +64301,7 @@
         <v>20260526</v>
       </c>
       <c r="K660" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L660" t="n">
         <v>0</v>
@@ -64111,7 +64394,7 @@
         <v>20260526</v>
       </c>
       <c r="K661" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L661" t="n">
         <v>0</v>
@@ -64204,7 +64487,7 @@
         <v>20260526</v>
       </c>
       <c r="K662" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L662" t="n">
         <v>0</v>
@@ -64297,7 +64580,7 @@
         <v>20260526</v>
       </c>
       <c r="K663" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L663" t="n">
         <v>0</v>
@@ -64390,7 +64673,7 @@
         <v>20260526</v>
       </c>
       <c r="K664" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L664" t="n">
         <v>0</v>
@@ -64483,7 +64766,7 @@
         <v>20260526</v>
       </c>
       <c r="K665" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L665" t="n">
         <v>0</v>
@@ -64576,7 +64859,7 @@
         <v>20260526</v>
       </c>
       <c r="K666" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L666" t="n">
         <v>0</v>
@@ -64669,7 +64952,7 @@
         <v>20260526</v>
       </c>
       <c r="K667" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L667" t="n">
         <v>0</v>
@@ -64762,7 +65045,7 @@
         <v>20260526</v>
       </c>
       <c r="K668" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L668" t="n">
         <v>0</v>
@@ -64855,7 +65138,7 @@
         <v>20260526</v>
       </c>
       <c r="K669" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L669" t="n">
         <v>0</v>
@@ -64948,7 +65231,7 @@
         <v>20260526</v>
       </c>
       <c r="K670" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L670" t="n">
         <v>0</v>
@@ -65041,7 +65324,7 @@
         <v>20260526</v>
       </c>
       <c r="K671" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L671" t="n">
         <v>0</v>
@@ -65134,7 +65417,7 @@
         <v>20260526</v>
       </c>
       <c r="K672" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L672" t="n">
         <v>0</v>
@@ -65227,7 +65510,7 @@
         <v>20260526</v>
       </c>
       <c r="K673" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L673" t="n">
         <v>0</v>
@@ -65320,7 +65603,7 @@
         <v>20260526</v>
       </c>
       <c r="K674" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L674" t="n">
         <v>300</v>
@@ -65413,7 +65696,7 @@
         <v>20260526</v>
       </c>
       <c r="K675" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L675" t="n">
         <v>300</v>
@@ -65506,7 +65789,7 @@
         <v>20260526</v>
       </c>
       <c r="K676" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L676" t="n">
         <v>300</v>
@@ -65599,7 +65882,7 @@
         <v>20260526</v>
       </c>
       <c r="K677" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L677" t="n">
         <v>300</v>
@@ -65692,7 +65975,7 @@
         <v>20260526</v>
       </c>
       <c r="K678" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L678" t="n">
         <v>600</v>
@@ -65785,7 +66068,7 @@
         <v>20260526</v>
       </c>
       <c r="K679" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L679" t="n">
         <v>600</v>
@@ -65878,7 +66161,7 @@
         <v>20260526</v>
       </c>
       <c r="K680" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L680" t="n">
         <v>600</v>
@@ -65971,7 +66254,7 @@
         <v>20260526</v>
       </c>
       <c r="K681" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L681" t="n">
         <v>600</v>
@@ -66064,7 +66347,7 @@
         <v>20260526</v>
       </c>
       <c r="K682" t="n">
-        <v>1779804607</v>
+        <v>1779805684</v>
       </c>
       <c r="L682" t="n">
         <v>600</v>

--- a/df_state.xlsx
+++ b/df_state.xlsx
@@ -587,7 +587,7 @@
         <v>20260527</v>
       </c>
       <c r="K2" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -680,7 +680,7 @@
         <v>20260527</v>
       </c>
       <c r="K3" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -773,7 +773,7 @@
         <v>20260527</v>
       </c>
       <c r="K4" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>20260527</v>
       </c>
       <c r="K5" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -959,7 +959,7 @@
         <v>20260527</v>
       </c>
       <c r="K6" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1052,7 +1052,7 @@
         <v>20260527</v>
       </c>
       <c r="K7" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>20260527</v>
       </c>
       <c r="K8" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L8" t="n">
         <v>300</v>
@@ -1238,7 +1238,7 @@
         <v>20260527</v>
       </c>
       <c r="K9" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>20260527</v>
       </c>
       <c r="K10" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>20260527</v>
       </c>
       <c r="K11" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1517,7 +1517,7 @@
         <v>20260527</v>
       </c>
       <c r="K12" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1610,7 +1610,7 @@
         <v>20260527</v>
       </c>
       <c r="K13" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>20260527</v>
       </c>
       <c r="K14" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>20260527</v>
       </c>
       <c r="K15" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1889,7 +1889,7 @@
         <v>20260527</v>
       </c>
       <c r="K16" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>20260527</v>
       </c>
       <c r="K17" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2075,7 +2075,7 @@
         <v>20260527</v>
       </c>
       <c r="K18" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2168,7 +2168,7 @@
         <v>20260527</v>
       </c>
       <c r="K19" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
         <v>20260527</v>
       </c>
       <c r="K20" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
         <v>20260527</v>
       </c>
       <c r="K21" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2447,7 +2447,7 @@
         <v>20260527</v>
       </c>
       <c r="K22" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>20260527</v>
       </c>
       <c r="K23" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>20260527</v>
       </c>
       <c r="K24" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>20260527</v>
       </c>
       <c r="K25" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2819,7 +2819,7 @@
         <v>20260527</v>
       </c>
       <c r="K26" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
         <v>20260527</v>
       </c>
       <c r="K27" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3005,7 +3005,7 @@
         <v>20260527</v>
       </c>
       <c r="K28" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3098,7 +3098,7 @@
         <v>20260527</v>
       </c>
       <c r="K29" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
         <v>20260527</v>
       </c>
       <c r="K30" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3284,7 +3284,7 @@
         <v>20260527</v>
       </c>
       <c r="K31" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         <v>20260527</v>
       </c>
       <c r="K32" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3470,7 +3470,7 @@
         <v>20260527</v>
       </c>
       <c r="K33" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -3563,7 +3563,7 @@
         <v>20260527</v>
       </c>
       <c r="K34" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
         <v>20260527</v>
       </c>
       <c r="K35" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>20260527</v>
       </c>
       <c r="K36" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3842,7 +3842,7 @@
         <v>20260527</v>
       </c>
       <c r="K37" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3935,7 +3935,7 @@
         <v>20260527</v>
       </c>
       <c r="K38" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4028,7 +4028,7 @@
         <v>20260527</v>
       </c>
       <c r="K39" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4121,7 +4121,7 @@
         <v>20260527</v>
       </c>
       <c r="K40" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4214,7 +4214,7 @@
         <v>20260527</v>
       </c>
       <c r="K41" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -4307,7 +4307,7 @@
         <v>20260527</v>
       </c>
       <c r="K42" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>20260527</v>
       </c>
       <c r="K43" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         <v>20260527</v>
       </c>
       <c r="K44" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -4586,7 +4586,7 @@
         <v>20260527</v>
       </c>
       <c r="K45" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>20260527</v>
       </c>
       <c r="K46" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -4772,7 +4772,7 @@
         <v>20260527</v>
       </c>
       <c r="K47" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
         <v>20260527</v>
       </c>
       <c r="K48" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
         <v>20260527</v>
       </c>
       <c r="K49" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -5051,7 +5051,7 @@
         <v>20260527</v>
       </c>
       <c r="K50" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
         <v>20260527</v>
       </c>
       <c r="K51" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -5237,7 +5237,7 @@
         <v>20260527</v>
       </c>
       <c r="K52" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -5330,7 +5330,7 @@
         <v>20260527</v>
       </c>
       <c r="K53" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L53" t="n">
         <v>300</v>
@@ -5423,7 +5423,7 @@
         <v>20260527</v>
       </c>
       <c r="K54" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
         <v>20260527</v>
       </c>
       <c r="K55" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -5609,7 +5609,7 @@
         <v>20260527</v>
       </c>
       <c r="K56" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -5702,7 +5702,7 @@
         <v>20260527</v>
       </c>
       <c r="K57" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -5795,7 +5795,7 @@
         <v>20260527</v>
       </c>
       <c r="K58" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -5888,7 +5888,7 @@
         <v>20260527</v>
       </c>
       <c r="K59" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -5981,7 +5981,7 @@
         <v>20260527</v>
       </c>
       <c r="K60" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -6074,7 +6074,7 @@
         <v>20260527</v>
       </c>
       <c r="K61" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
         <v>20260527</v>
       </c>
       <c r="K62" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -6260,7 +6260,7 @@
         <v>20260527</v>
       </c>
       <c r="K63" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -6353,7 +6353,7 @@
         <v>20260527</v>
       </c>
       <c r="K64" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
         <v>20260527</v>
       </c>
       <c r="K65" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -6539,7 +6539,7 @@
         <v>20260527</v>
       </c>
       <c r="K66" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -6632,7 +6632,7 @@
         <v>20260527</v>
       </c>
       <c r="K67" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
         <v>20260527</v>
       </c>
       <c r="K68" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -6818,7 +6818,7 @@
         <v>20260527</v>
       </c>
       <c r="K69" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -6911,7 +6911,7 @@
         <v>20260527</v>
       </c>
       <c r="K70" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
         <v>20260527</v>
       </c>
       <c r="K71" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>20260527</v>
       </c>
       <c r="K72" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -7190,7 +7190,7 @@
         <v>20260527</v>
       </c>
       <c r="K73" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -7283,7 +7283,7 @@
         <v>20260527</v>
       </c>
       <c r="K74" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
         <v>20260527</v>
       </c>
       <c r="K75" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -7469,7 +7469,7 @@
         <v>20260527</v>
       </c>
       <c r="K76" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -7562,7 +7562,7 @@
         <v>20260527</v>
       </c>
       <c r="K77" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>20260527</v>
       </c>
       <c r="K78" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -7748,7 +7748,7 @@
         <v>20260527</v>
       </c>
       <c r="K79" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -7841,7 +7841,7 @@
         <v>20260527</v>
       </c>
       <c r="K80" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -7934,7 +7934,7 @@
         <v>20260527</v>
       </c>
       <c r="K81" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>20260527</v>
       </c>
       <c r="K82" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
         <v>20260527</v>
       </c>
       <c r="K83" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -8213,7 +8213,7 @@
         <v>20260527</v>
       </c>
       <c r="K84" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -8306,7 +8306,7 @@
         <v>20260527</v>
       </c>
       <c r="K85" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -8399,7 +8399,7 @@
         <v>20260527</v>
       </c>
       <c r="K86" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -8492,7 +8492,7 @@
         <v>20260527</v>
       </c>
       <c r="K87" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
         <v>20260527</v>
       </c>
       <c r="K88" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -8678,7 +8678,7 @@
         <v>20260527</v>
       </c>
       <c r="K89" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
         <v>20260527</v>
       </c>
       <c r="K90" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
         <v>20260527</v>
       </c>
       <c r="K91" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -8957,7 +8957,7 @@
         <v>20260527</v>
       </c>
       <c r="K92" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -9050,7 +9050,7 @@
         <v>20260527</v>
       </c>
       <c r="K93" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
         <v>20260527</v>
       </c>
       <c r="K94" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -9236,7 +9236,7 @@
         <v>20260527</v>
       </c>
       <c r="K95" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -9329,7 +9329,7 @@
         <v>20260527</v>
       </c>
       <c r="K96" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -9422,7 +9422,7 @@
         <v>20260527</v>
       </c>
       <c r="K97" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -9515,7 +9515,7 @@
         <v>20260527</v>
       </c>
       <c r="K98" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -9608,7 +9608,7 @@
         <v>20260527</v>
       </c>
       <c r="K99" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -9701,7 +9701,7 @@
         <v>20260527</v>
       </c>
       <c r="K100" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>20260527</v>
       </c>
       <c r="K101" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -9887,7 +9887,7 @@
         <v>20260527</v>
       </c>
       <c r="K102" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -9980,7 +9980,7 @@
         <v>20260527</v>
       </c>
       <c r="K103" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -10073,7 +10073,7 @@
         <v>20260527</v>
       </c>
       <c r="K104" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -10166,7 +10166,7 @@
         <v>20260527</v>
       </c>
       <c r="K105" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -10259,7 +10259,7 @@
         <v>20260527</v>
       </c>
       <c r="K106" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -10352,7 +10352,7 @@
         <v>20260527</v>
       </c>
       <c r="K107" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -10445,7 +10445,7 @@
         <v>20260527</v>
       </c>
       <c r="K108" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
         <v>20260527</v>
       </c>
       <c r="K109" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -10631,7 +10631,7 @@
         <v>20260527</v>
       </c>
       <c r="K110" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -10724,7 +10724,7 @@
         <v>20260527</v>
       </c>
       <c r="K111" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -10817,7 +10817,7 @@
         <v>20260527</v>
       </c>
       <c r="K112" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -10910,7 +10910,7 @@
         <v>20260527</v>
       </c>
       <c r="K113" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -11003,7 +11003,7 @@
         <v>20260527</v>
       </c>
       <c r="K114" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -11096,7 +11096,7 @@
         <v>20260527</v>
       </c>
       <c r="K115" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -11189,7 +11189,7 @@
         <v>20260527</v>
       </c>
       <c r="K116" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -11282,7 +11282,7 @@
         <v>20260527</v>
       </c>
       <c r="K117" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -11375,7 +11375,7 @@
         <v>20260527</v>
       </c>
       <c r="K118" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -11468,7 +11468,7 @@
         <v>20260527</v>
       </c>
       <c r="K119" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -11561,7 +11561,7 @@
         <v>20260527</v>
       </c>
       <c r="K120" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>20260527</v>
       </c>
       <c r="K121" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -11747,7 +11747,7 @@
         <v>20260527</v>
       </c>
       <c r="K122" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -11840,7 +11840,7 @@
         <v>20260527</v>
       </c>
       <c r="K123" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -11933,7 +11933,7 @@
         <v>20260527</v>
       </c>
       <c r="K124" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -12026,7 +12026,7 @@
         <v>20260527</v>
       </c>
       <c r="K125" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -12119,7 +12119,7 @@
         <v>20260527</v>
       </c>
       <c r="K126" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -12212,7 +12212,7 @@
         <v>20260527</v>
       </c>
       <c r="K127" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L127" t="n">
         <v>300</v>
@@ -12305,7 +12305,7 @@
         <v>20260527</v>
       </c>
       <c r="K128" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L128" t="n">
         <v>300</v>
@@ -12398,7 +12398,7 @@
         <v>20260527</v>
       </c>
       <c r="K129" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L129" t="n">
         <v>300</v>
@@ -12491,7 +12491,7 @@
         <v>20260527</v>
       </c>
       <c r="K130" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -12584,7 +12584,7 @@
         <v>20260527</v>
       </c>
       <c r="K131" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -12677,7 +12677,7 @@
         <v>20260527</v>
       </c>
       <c r="K132" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
         <v>20260527</v>
       </c>
       <c r="K133" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -12863,7 +12863,7 @@
         <v>20260527</v>
       </c>
       <c r="K134" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -12956,7 +12956,7 @@
         <v>20260527</v>
       </c>
       <c r="K135" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -13049,7 +13049,7 @@
         <v>20260527</v>
       </c>
       <c r="K136" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -13142,7 +13142,7 @@
         <v>20260527</v>
       </c>
       <c r="K137" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -13235,7 +13235,7 @@
         <v>20260527</v>
       </c>
       <c r="K138" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -13328,7 +13328,7 @@
         <v>20260527</v>
       </c>
       <c r="K139" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -13421,7 +13421,7 @@
         <v>20260527</v>
       </c>
       <c r="K140" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -13514,7 +13514,7 @@
         <v>20260527</v>
       </c>
       <c r="K141" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -13607,7 +13607,7 @@
         <v>20260527</v>
       </c>
       <c r="K142" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -13700,7 +13700,7 @@
         <v>20260527</v>
       </c>
       <c r="K143" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -13793,7 +13793,7 @@
         <v>20260527</v>
       </c>
       <c r="K144" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -13886,7 +13886,7 @@
         <v>20260527</v>
       </c>
       <c r="K145" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -13979,7 +13979,7 @@
         <v>20260527</v>
       </c>
       <c r="K146" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -14072,7 +14072,7 @@
         <v>20260527</v>
       </c>
       <c r="K147" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -14165,7 +14165,7 @@
         <v>20260527</v>
       </c>
       <c r="K148" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -14258,7 +14258,7 @@
         <v>20260527</v>
       </c>
       <c r="K149" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -14351,7 +14351,7 @@
         <v>20260527</v>
       </c>
       <c r="K150" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -14444,7 +14444,7 @@
         <v>20260527</v>
       </c>
       <c r="K151" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -14537,7 +14537,7 @@
         <v>20260527</v>
       </c>
       <c r="K152" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
         <v>20260527</v>
       </c>
       <c r="K153" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -14723,7 +14723,7 @@
         <v>20260527</v>
       </c>
       <c r="K154" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -14816,7 +14816,7 @@
         <v>20260527</v>
       </c>
       <c r="K155" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -14909,7 +14909,7 @@
         <v>20260527</v>
       </c>
       <c r="K156" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -15002,7 +15002,7 @@
         <v>20260527</v>
       </c>
       <c r="K157" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -15095,7 +15095,7 @@
         <v>20260527</v>
       </c>
       <c r="K158" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>20260527</v>
       </c>
       <c r="K159" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -15281,7 +15281,7 @@
         <v>20260527</v>
       </c>
       <c r="K160" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -15374,7 +15374,7 @@
         <v>20260527</v>
       </c>
       <c r="K161" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -15467,7 +15467,7 @@
         <v>20260527</v>
       </c>
       <c r="K162" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L162" t="n">
         <v>600</v>
@@ -15560,7 +15560,7 @@
         <v>20260527</v>
       </c>
       <c r="K163" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>20260527</v>
       </c>
       <c r="K164" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -15746,7 +15746,7 @@
         <v>20260527</v>
       </c>
       <c r="K165" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -15839,7 +15839,7 @@
         <v>20260527</v>
       </c>
       <c r="K166" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -15932,7 +15932,7 @@
         <v>20260527</v>
       </c>
       <c r="K167" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -16025,7 +16025,7 @@
         <v>20260527</v>
       </c>
       <c r="K168" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -16118,7 +16118,7 @@
         <v>20260527</v>
       </c>
       <c r="K169" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -16211,7 +16211,7 @@
         <v>20260527</v>
       </c>
       <c r="K170" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -16304,7 +16304,7 @@
         <v>20260527</v>
       </c>
       <c r="K171" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -16397,7 +16397,7 @@
         <v>20260527</v>
       </c>
       <c r="K172" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -16490,7 +16490,7 @@
         <v>20260527</v>
       </c>
       <c r="K173" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
         <v>20260527</v>
       </c>
       <c r="K174" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -16676,7 +16676,7 @@
         <v>20260527</v>
       </c>
       <c r="K175" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -16769,7 +16769,7 @@
         <v>20260527</v>
       </c>
       <c r="K176" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -16862,7 +16862,7 @@
         <v>20260527</v>
       </c>
       <c r="K177" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -16955,7 +16955,7 @@
         <v>20260527</v>
       </c>
       <c r="K178" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -17048,7 +17048,7 @@
         <v>20260527</v>
       </c>
       <c r="K179" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -17141,7 +17141,7 @@
         <v>20260527</v>
       </c>
       <c r="K180" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -17234,7 +17234,7 @@
         <v>20260527</v>
       </c>
       <c r="K181" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -17327,7 +17327,7 @@
         <v>20260527</v>
       </c>
       <c r="K182" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -17420,7 +17420,7 @@
         <v>20260527</v>
       </c>
       <c r="K183" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -17513,7 +17513,7 @@
         <v>20260527</v>
       </c>
       <c r="K184" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -17606,7 +17606,7 @@
         <v>20260527</v>
       </c>
       <c r="K185" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -17699,7 +17699,7 @@
         <v>20260527</v>
       </c>
       <c r="K186" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -17792,7 +17792,7 @@
         <v>20260527</v>
       </c>
       <c r="K187" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -17885,7 +17885,7 @@
         <v>20260527</v>
       </c>
       <c r="K188" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -17978,7 +17978,7 @@
         <v>20260527</v>
       </c>
       <c r="K189" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -18071,7 +18071,7 @@
         <v>20260527</v>
       </c>
       <c r="K190" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -18164,7 +18164,7 @@
         <v>20260527</v>
       </c>
       <c r="K191" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -18257,7 +18257,7 @@
         <v>20260527</v>
       </c>
       <c r="K192" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -18350,7 +18350,7 @@
         <v>20260527</v>
       </c>
       <c r="K193" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -18376,11 +18376,11 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>finished</t>
         </is>
       </c>
       <c r="S193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T193" t="b">
         <v>0</v>
@@ -18443,7 +18443,7 @@
         <v>20260527</v>
       </c>
       <c r="K194" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -18469,11 +18469,11 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>finished</t>
         </is>
       </c>
       <c r="S194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T194" t="b">
         <v>0</v>
@@ -18536,7 +18536,7 @@
         <v>20260527</v>
       </c>
       <c r="K195" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -18629,7 +18629,7 @@
         <v>20260527</v>
       </c>
       <c r="K196" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
         <v>20260527</v>
       </c>
       <c r="K197" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -18815,7 +18815,7 @@
         <v>20260527</v>
       </c>
       <c r="K198" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -18908,7 +18908,7 @@
         <v>20260527</v>
       </c>
       <c r="K199" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -19001,7 +19001,7 @@
         <v>20260527</v>
       </c>
       <c r="K200" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -19094,7 +19094,7 @@
         <v>20260527</v>
       </c>
       <c r="K201" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
         <v>20260527</v>
       </c>
       <c r="K202" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -19280,7 +19280,7 @@
         <v>20260527</v>
       </c>
       <c r="K203" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -19373,7 +19373,7 @@
         <v>20260527</v>
       </c>
       <c r="K204" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -19466,7 +19466,7 @@
         <v>20260527</v>
       </c>
       <c r="K205" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -19559,7 +19559,7 @@
         <v>20260527</v>
       </c>
       <c r="K206" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -19652,7 +19652,7 @@
         <v>20260527</v>
       </c>
       <c r="K207" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -19745,7 +19745,7 @@
         <v>20260527</v>
       </c>
       <c r="K208" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -19838,7 +19838,7 @@
         <v>20260527</v>
       </c>
       <c r="K209" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -19931,7 +19931,7 @@
         <v>20260527</v>
       </c>
       <c r="K210" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>20260527</v>
       </c>
       <c r="K211" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -20117,7 +20117,7 @@
         <v>20260527</v>
       </c>
       <c r="K212" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -20210,7 +20210,7 @@
         <v>20260527</v>
       </c>
       <c r="K213" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L213" t="n">
         <v>0</v>
@@ -20303,7 +20303,7 @@
         <v>20260527</v>
       </c>
       <c r="K214" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -20396,7 +20396,7 @@
         <v>20260527</v>
       </c>
       <c r="K215" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -20489,7 +20489,7 @@
         <v>20260527</v>
       </c>
       <c r="K216" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -20582,7 +20582,7 @@
         <v>20260527</v>
       </c>
       <c r="K217" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -20675,7 +20675,7 @@
         <v>20260527</v>
       </c>
       <c r="K218" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -20768,7 +20768,7 @@
         <v>20260527</v>
       </c>
       <c r="K219" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -20861,7 +20861,7 @@
         <v>20260527</v>
       </c>
       <c r="K220" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -20954,7 +20954,7 @@
         <v>20260527</v>
       </c>
       <c r="K221" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>
@@ -21047,7 +21047,7 @@
         <v>20260527</v>
       </c>
       <c r="K222" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
@@ -21140,7 +21140,7 @@
         <v>20260527</v>
       </c>
       <c r="K223" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L223" t="n">
         <v>0</v>
@@ -21233,7 +21233,7 @@
         <v>20260527</v>
       </c>
       <c r="K224" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -21326,7 +21326,7 @@
         <v>20260527</v>
       </c>
       <c r="K225" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L225" t="n">
         <v>0</v>
@@ -21419,7 +21419,7 @@
         <v>20260527</v>
       </c>
       <c r="K226" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -21512,7 +21512,7 @@
         <v>20260527</v>
       </c>
       <c r="K227" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L227" t="n">
         <v>900</v>
@@ -21605,7 +21605,7 @@
         <v>20260527</v>
       </c>
       <c r="K228" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L228" t="n">
         <v>900</v>
@@ -21698,7 +21698,7 @@
         <v>20260527</v>
       </c>
       <c r="K229" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L229" t="n">
         <v>600</v>
@@ -21791,7 +21791,7 @@
         <v>20260527</v>
       </c>
       <c r="K230" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -21836,21 +21836,9 @@
           <t>OCESN2807F1187_F:OUI:FR:Line::6E3CCD81-9398-44C3-9D79-072A8303E507::87113001:82001000:5:1033</t>
         </is>
       </c>
-      <c r="W230" t="inlineStr">
-        <is>
-          <t>retard de votre rame lors de son précédent trajet .</t>
-        </is>
-      </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>Votre train est retardé</t>
-        </is>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>Cause : retard de votre rame lors de son précédent trajet .</t>
-        </is>
-      </c>
+      <c r="W230" t="inlineStr"/>
+      <c r="X230" t="inlineStr"/>
+      <c r="Y230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -21896,7 +21884,7 @@
         <v>20260527</v>
       </c>
       <c r="K231" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L231" t="n">
         <v>1800</v>
@@ -21941,21 +21929,9 @@
           <t>OCESN2807F1187_F:OUI:FR:Line::6E3CCD81-9398-44C3-9D79-072A8303E507::87113001:82001000:5:1033</t>
         </is>
       </c>
-      <c r="W231" t="inlineStr">
-        <is>
-          <t>retard de votre rame lors de son précédent trajet .</t>
-        </is>
-      </c>
-      <c r="X231" t="inlineStr">
-        <is>
-          <t>Votre train est retardé</t>
-        </is>
-      </c>
-      <c r="Y231" t="inlineStr">
-        <is>
-          <t>Cause : retard de votre rame lors de son précédent trajet .</t>
-        </is>
-      </c>
+      <c r="W231" t="inlineStr"/>
+      <c r="X231" t="inlineStr"/>
+      <c r="Y231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -22001,7 +21977,7 @@
         <v>20260527</v>
       </c>
       <c r="K232" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L232" t="n">
         <v>1800</v>
@@ -22046,21 +22022,9 @@
           <t>OCESN2807F1187_F:OUI:FR:Line::6E3CCD81-9398-44C3-9D79-072A8303E507::87113001:82001000:5:1033</t>
         </is>
       </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>retard de votre rame lors de son précédent trajet .</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Votre train est retardé</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>Cause : retard de votre rame lors de son précédent trajet .</t>
-        </is>
-      </c>
+      <c r="W232" t="inlineStr"/>
+      <c r="X232" t="inlineStr"/>
+      <c r="Y232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -22106,7 +22070,7 @@
         <v>20260527</v>
       </c>
       <c r="K233" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L233" t="n">
         <v>1800</v>
@@ -22151,21 +22115,9 @@
           <t>OCESN2807F1187_F:OUI:FR:Line::6E3CCD81-9398-44C3-9D79-072A8303E507::87113001:82001000:5:1033</t>
         </is>
       </c>
-      <c r="W233" t="inlineStr">
-        <is>
-          <t>retard de votre rame lors de son précédent trajet .</t>
-        </is>
-      </c>
-      <c r="X233" t="inlineStr">
-        <is>
-          <t>Votre train est retardé</t>
-        </is>
-      </c>
-      <c r="Y233" t="inlineStr">
-        <is>
-          <t>Cause : retard de votre rame lors de son précédent trajet .</t>
-        </is>
-      </c>
+      <c r="W233" t="inlineStr"/>
+      <c r="X233" t="inlineStr"/>
+      <c r="Y233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -22211,7 +22163,7 @@
         <v>20260527</v>
       </c>
       <c r="K234" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L234" t="n">
         <v>1800</v>
@@ -22256,21 +22208,9 @@
           <t>OCESN2807F1187_F:OUI:FR:Line::6E3CCD81-9398-44C3-9D79-072A8303E507::87113001:82001000:5:1033</t>
         </is>
       </c>
-      <c r="W234" t="inlineStr">
-        <is>
-          <t>retard de votre rame lors de son précédent trajet .</t>
-        </is>
-      </c>
-      <c r="X234" t="inlineStr">
-        <is>
-          <t>Votre train est retardé</t>
-        </is>
-      </c>
-      <c r="Y234" t="inlineStr">
-        <is>
-          <t>Cause : retard de votre rame lors de son précédent trajet .</t>
-        </is>
-      </c>
+      <c r="W234" t="inlineStr"/>
+      <c r="X234" t="inlineStr"/>
+      <c r="Y234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -22316,7 +22256,7 @@
         <v>20260527</v>
       </c>
       <c r="K235" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -22409,7 +22349,7 @@
         <v>20260527</v>
       </c>
       <c r="K236" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -22502,7 +22442,7 @@
         <v>20260527</v>
       </c>
       <c r="K237" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -22595,7 +22535,7 @@
         <v>20260527</v>
       </c>
       <c r="K238" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -22688,7 +22628,7 @@
         <v>20260527</v>
       </c>
       <c r="K239" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -22781,7 +22721,7 @@
         <v>20260527</v>
       </c>
       <c r="K240" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -22874,7 +22814,7 @@
         <v>20260527</v>
       </c>
       <c r="K241" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -22967,7 +22907,7 @@
         <v>20260527</v>
       </c>
       <c r="K242" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -23060,7 +23000,7 @@
         <v>20260527</v>
       </c>
       <c r="K243" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -23153,7 +23093,7 @@
         <v>20260527</v>
       </c>
       <c r="K244" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -23246,7 +23186,7 @@
         <v>20260527</v>
       </c>
       <c r="K245" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -23339,7 +23279,7 @@
         <v>20260527</v>
       </c>
       <c r="K246" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -23432,7 +23372,7 @@
         <v>20260527</v>
       </c>
       <c r="K247" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -23525,7 +23465,7 @@
         <v>20260527</v>
       </c>
       <c r="K248" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -23618,7 +23558,7 @@
         <v>20260527</v>
       </c>
       <c r="K249" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -23711,7 +23651,7 @@
         <v>20260527</v>
       </c>
       <c r="K250" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -23804,7 +23744,7 @@
         <v>20260527</v>
       </c>
       <c r="K251" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L251" t="n">
         <v>0</v>
@@ -23897,7 +23837,7 @@
         <v>20260527</v>
       </c>
       <c r="K252" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L252" t="n">
         <v>1500</v>
@@ -23990,7 +23930,7 @@
         <v>20260527</v>
       </c>
       <c r="K253" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L253" t="n">
         <v>1500</v>
@@ -24083,7 +24023,7 @@
         <v>20260527</v>
       </c>
       <c r="K254" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L254" t="n">
         <v>1800</v>
@@ -24176,7 +24116,7 @@
         <v>20260527</v>
       </c>
       <c r="K255" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -24269,7 +24209,7 @@
         <v>20260527</v>
       </c>
       <c r="K256" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -24362,7 +24302,7 @@
         <v>20260527</v>
       </c>
       <c r="K257" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -24455,7 +24395,7 @@
         <v>20260527</v>
       </c>
       <c r="K258" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L258" t="n">
         <v>0</v>
@@ -24548,7 +24488,7 @@
         <v>20260527</v>
       </c>
       <c r="K259" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -24641,7 +24581,7 @@
         <v>20260527</v>
       </c>
       <c r="K260" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>
@@ -24734,7 +24674,7 @@
         <v>20260527</v>
       </c>
       <c r="K261" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L261" t="n">
         <v>0</v>
@@ -24827,7 +24767,7 @@
         <v>20260527</v>
       </c>
       <c r="K262" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L262" t="n">
         <v>0</v>
@@ -24920,7 +24860,7 @@
         <v>20260527</v>
       </c>
       <c r="K263" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -25013,7 +24953,7 @@
         <v>20260527</v>
       </c>
       <c r="K264" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L264" t="n">
         <v>0</v>
@@ -25106,7 +25046,7 @@
         <v>20260527</v>
       </c>
       <c r="K265" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L265" t="n">
         <v>0</v>
@@ -25199,7 +25139,7 @@
         <v>20260527</v>
       </c>
       <c r="K266" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L266" t="n">
         <v>0</v>
@@ -25292,7 +25232,7 @@
         <v>20260527</v>
       </c>
       <c r="K267" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L267" t="n">
         <v>0</v>
@@ -25385,7 +25325,7 @@
         <v>20260527</v>
       </c>
       <c r="K268" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L268" t="n">
         <v>0</v>
@@ -25478,7 +25418,7 @@
         <v>20260527</v>
       </c>
       <c r="K269" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L269" t="n">
         <v>0</v>
@@ -25571,7 +25511,7 @@
         <v>20260527</v>
       </c>
       <c r="K270" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -25664,7 +25604,7 @@
         <v>20260527</v>
       </c>
       <c r="K271" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L271" t="n">
         <v>0</v>
@@ -25757,7 +25697,7 @@
         <v>20260527</v>
       </c>
       <c r="K272" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L272" t="n">
         <v>0</v>
@@ -25850,7 +25790,7 @@
         <v>20260527</v>
       </c>
       <c r="K273" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L273" t="n">
         <v>0</v>
@@ -25943,7 +25883,7 @@
         <v>20260527</v>
       </c>
       <c r="K274" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L274" t="n">
         <v>0</v>
@@ -26036,7 +25976,7 @@
         <v>20260527</v>
       </c>
       <c r="K275" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L275" t="n">
         <v>0</v>
@@ -26129,7 +26069,7 @@
         <v>20260527</v>
       </c>
       <c r="K276" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L276" t="n">
         <v>0</v>
@@ -26222,7 +26162,7 @@
         <v>20260527</v>
       </c>
       <c r="K277" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L277" t="n">
         <v>0</v>
@@ -26315,7 +26255,7 @@
         <v>20260527</v>
       </c>
       <c r="K278" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
@@ -26408,7 +26348,7 @@
         <v>20260527</v>
       </c>
       <c r="K279" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L279" t="n">
         <v>0</v>
@@ -26501,7 +26441,7 @@
         <v>20260527</v>
       </c>
       <c r="K280" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L280" t="n">
         <v>0</v>
@@ -26594,7 +26534,7 @@
         <v>20260527</v>
       </c>
       <c r="K281" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L281" t="n">
         <v>0</v>
@@ -26687,7 +26627,7 @@
         <v>20260527</v>
       </c>
       <c r="K282" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L282" t="n">
         <v>0</v>
@@ -26780,7 +26720,7 @@
         <v>20260527</v>
       </c>
       <c r="K283" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L283" t="n">
         <v>0</v>
@@ -26873,7 +26813,7 @@
         <v>20260527</v>
       </c>
       <c r="K284" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L284" t="n">
         <v>0</v>
@@ -26966,7 +26906,7 @@
         <v>20260527</v>
       </c>
       <c r="K285" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L285" t="n">
         <v>0</v>
@@ -27059,7 +26999,7 @@
         <v>20260527</v>
       </c>
       <c r="K286" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L286" t="n">
         <v>0</v>
@@ -27152,7 +27092,7 @@
         <v>20260527</v>
       </c>
       <c r="K287" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L287" t="n">
         <v>0</v>
@@ -27245,7 +27185,7 @@
         <v>20260527</v>
       </c>
       <c r="K288" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L288" t="n">
         <v>0</v>
@@ -27338,7 +27278,7 @@
         <v>20260527</v>
       </c>
       <c r="K289" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L289" t="n">
         <v>0</v>
@@ -27431,7 +27371,7 @@
         <v>20260527</v>
       </c>
       <c r="K290" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L290" t="n">
         <v>0</v>
@@ -27524,7 +27464,7 @@
         <v>20260527</v>
       </c>
       <c r="K291" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L291" t="n">
         <v>0</v>
@@ -27617,7 +27557,7 @@
         <v>20260527</v>
       </c>
       <c r="K292" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L292" t="n">
         <v>0</v>
@@ -27710,7 +27650,7 @@
         <v>20260527</v>
       </c>
       <c r="K293" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L293" t="n">
         <v>0</v>
@@ -27803,7 +27743,7 @@
         <v>20260527</v>
       </c>
       <c r="K294" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L294" t="n">
         <v>0</v>
@@ -27896,7 +27836,7 @@
         <v>20260527</v>
       </c>
       <c r="K295" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -27989,7 +27929,7 @@
         <v>20260527</v>
       </c>
       <c r="K296" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L296" t="n">
         <v>0</v>
@@ -28082,7 +28022,7 @@
         <v>20260527</v>
       </c>
       <c r="K297" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L297" t="n">
         <v>0</v>
@@ -28175,7 +28115,7 @@
         <v>20260527</v>
       </c>
       <c r="K298" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L298" t="n">
         <v>0</v>
@@ -28268,7 +28208,7 @@
         <v>20260527</v>
       </c>
       <c r="K299" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L299" t="n">
         <v>0</v>
@@ -28361,7 +28301,7 @@
         <v>20260527</v>
       </c>
       <c r="K300" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L300" t="n">
         <v>0</v>
@@ -28454,7 +28394,7 @@
         <v>20260527</v>
       </c>
       <c r="K301" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L301" t="n">
         <v>0</v>
@@ -28547,7 +28487,7 @@
         <v>20260527</v>
       </c>
       <c r="K302" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L302" t="n">
         <v>0</v>
@@ -28640,7 +28580,7 @@
         <v>20260527</v>
       </c>
       <c r="K303" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L303" t="n">
         <v>0</v>
@@ -28733,7 +28673,7 @@
         <v>20260527</v>
       </c>
       <c r="K304" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L304" t="n">
         <v>0</v>
@@ -28826,7 +28766,7 @@
         <v>20260527</v>
       </c>
       <c r="K305" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L305" t="n">
         <v>0</v>
@@ -28919,7 +28859,7 @@
         <v>20260527</v>
       </c>
       <c r="K306" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L306" t="n">
         <v>0</v>
@@ -29012,7 +28952,7 @@
         <v>20260527</v>
       </c>
       <c r="K307" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L307" t="n">
         <v>0</v>
@@ -29105,7 +29045,7 @@
         <v>20260527</v>
       </c>
       <c r="K308" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L308" t="n">
         <v>0</v>
@@ -29198,7 +29138,7 @@
         <v>20260527</v>
       </c>
       <c r="K309" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L309" t="n">
         <v>0</v>
@@ -29291,7 +29231,7 @@
         <v>20260527</v>
       </c>
       <c r="K310" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L310" t="n">
         <v>0</v>
@@ -29384,7 +29324,7 @@
         <v>20260527</v>
       </c>
       <c r="K311" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L311" t="n">
         <v>0</v>
@@ -29477,7 +29417,7 @@
         <v>20260527</v>
       </c>
       <c r="K312" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L312" t="n">
         <v>0</v>
@@ -29570,7 +29510,7 @@
         <v>20260527</v>
       </c>
       <c r="K313" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L313" t="n">
         <v>0</v>
@@ -29663,7 +29603,7 @@
         <v>20260527</v>
       </c>
       <c r="K314" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L314" t="n">
         <v>0</v>
@@ -29756,7 +29696,7 @@
         <v>20260527</v>
       </c>
       <c r="K315" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L315" t="n">
         <v>0</v>
@@ -29849,7 +29789,7 @@
         <v>20260527</v>
       </c>
       <c r="K316" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L316" t="n">
         <v>0</v>
@@ -29942,7 +29882,7 @@
         <v>20260527</v>
       </c>
       <c r="K317" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L317" t="n">
         <v>0</v>
@@ -30035,7 +29975,7 @@
         <v>20260527</v>
       </c>
       <c r="K318" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L318" t="n">
         <v>0</v>
@@ -30128,7 +30068,7 @@
         <v>20260527</v>
       </c>
       <c r="K319" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L319" t="n">
         <v>0</v>
@@ -30221,7 +30161,7 @@
         <v>20260527</v>
       </c>
       <c r="K320" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L320" t="n">
         <v>0</v>
@@ -30314,7 +30254,7 @@
         <v>20260527</v>
       </c>
       <c r="K321" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L321" t="n">
         <v>0</v>
@@ -30407,7 +30347,7 @@
         <v>20260527</v>
       </c>
       <c r="K322" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L322" t="n">
         <v>0</v>
@@ -30500,7 +30440,7 @@
         <v>20260527</v>
       </c>
       <c r="K323" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L323" t="n">
         <v>0</v>
@@ -30593,7 +30533,7 @@
         <v>20260527</v>
       </c>
       <c r="K324" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L324" t="n">
         <v>0</v>
@@ -30686,7 +30626,7 @@
         <v>20260527</v>
       </c>
       <c r="K325" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L325" t="n">
         <v>0</v>
@@ -30779,7 +30719,7 @@
         <v>20260527</v>
       </c>
       <c r="K326" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L326" t="n">
         <v>0</v>
@@ -30872,7 +30812,7 @@
         <v>20260527</v>
       </c>
       <c r="K327" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L327" t="n">
         <v>0</v>
@@ -30965,7 +30905,7 @@
         <v>20260527</v>
       </c>
       <c r="K328" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L328" t="n">
         <v>0</v>
@@ -31058,7 +30998,7 @@
         <v>20260527</v>
       </c>
       <c r="K329" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L329" t="n">
         <v>0</v>
@@ -31151,7 +31091,7 @@
         <v>20260527</v>
       </c>
       <c r="K330" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L330" t="n">
         <v>300</v>
@@ -31244,7 +31184,7 @@
         <v>20260527</v>
       </c>
       <c r="K331" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L331" t="n">
         <v>0</v>
@@ -31337,7 +31277,7 @@
         <v>20260527</v>
       </c>
       <c r="K332" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L332" t="n">
         <v>0</v>
@@ -31430,7 +31370,7 @@
         <v>20260527</v>
       </c>
       <c r="K333" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L333" t="n">
         <v>0</v>
@@ -31523,7 +31463,7 @@
         <v>20260527</v>
       </c>
       <c r="K334" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L334" t="n">
         <v>0</v>
@@ -31616,7 +31556,7 @@
         <v>20260527</v>
       </c>
       <c r="K335" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L335" t="n">
         <v>0</v>
@@ -31709,7 +31649,7 @@
         <v>20260527</v>
       </c>
       <c r="K336" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L336" t="n">
         <v>0</v>
@@ -31802,7 +31742,7 @@
         <v>20260527</v>
       </c>
       <c r="K337" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L337" t="n">
         <v>0</v>
@@ -31895,7 +31835,7 @@
         <v>20260527</v>
       </c>
       <c r="K338" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L338" t="n">
         <v>0</v>
@@ -31988,7 +31928,7 @@
         <v>20260527</v>
       </c>
       <c r="K339" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L339" t="n">
         <v>0</v>
@@ -32081,7 +32021,7 @@
         <v>20260527</v>
       </c>
       <c r="K340" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L340" t="n">
         <v>0</v>
@@ -32174,7 +32114,7 @@
         <v>20260527</v>
       </c>
       <c r="K341" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L341" t="n">
         <v>0</v>
@@ -32267,7 +32207,7 @@
         <v>20260527</v>
       </c>
       <c r="K342" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L342" t="n">
         <v>0</v>
@@ -32360,7 +32300,7 @@
         <v>20260527</v>
       </c>
       <c r="K343" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L343" t="n">
         <v>0</v>
@@ -32453,7 +32393,7 @@
         <v>20260527</v>
       </c>
       <c r="K344" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L344" t="n">
         <v>0</v>
@@ -32546,7 +32486,7 @@
         <v>20260527</v>
       </c>
       <c r="K345" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L345" t="n">
         <v>0</v>
@@ -32639,7 +32579,7 @@
         <v>20260527</v>
       </c>
       <c r="K346" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L346" t="n">
         <v>0</v>
@@ -32732,7 +32672,7 @@
         <v>20260527</v>
       </c>
       <c r="K347" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L347" t="n">
         <v>0</v>
@@ -32825,7 +32765,7 @@
         <v>20260527</v>
       </c>
       <c r="K348" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L348" t="n">
         <v>0</v>
@@ -32918,7 +32858,7 @@
         <v>20260527</v>
       </c>
       <c r="K349" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L349" t="n">
         <v>0</v>
@@ -33011,7 +32951,7 @@
         <v>20260527</v>
       </c>
       <c r="K350" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L350" t="n">
         <v>0</v>
@@ -33104,7 +33044,7 @@
         <v>20260527</v>
       </c>
       <c r="K351" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L351" t="n">
         <v>0</v>
@@ -33197,7 +33137,7 @@
         <v>20260527</v>
       </c>
       <c r="K352" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L352" t="n">
         <v>0</v>
@@ -33290,7 +33230,7 @@
         <v>20260527</v>
       </c>
       <c r="K353" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L353" t="n">
         <v>0</v>
@@ -33383,7 +33323,7 @@
         <v>20260527</v>
       </c>
       <c r="K354" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L354" t="n">
         <v>0</v>
@@ -33476,7 +33416,7 @@
         <v>20260527</v>
       </c>
       <c r="K355" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L355" t="n">
         <v>0</v>
@@ -33569,7 +33509,7 @@
         <v>20260527</v>
       </c>
       <c r="K356" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L356" t="n">
         <v>0</v>
@@ -33662,7 +33602,7 @@
         <v>20260527</v>
       </c>
       <c r="K357" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L357" t="n">
         <v>0</v>
@@ -33755,7 +33695,7 @@
         <v>20260527</v>
       </c>
       <c r="K358" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L358" t="n">
         <v>0</v>
@@ -33848,7 +33788,7 @@
         <v>20260527</v>
       </c>
       <c r="K359" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L359" t="n">
         <v>0</v>
@@ -33941,7 +33881,7 @@
         <v>20260527</v>
       </c>
       <c r="K360" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L360" t="n">
         <v>0</v>
@@ -34034,7 +33974,7 @@
         <v>20260527</v>
       </c>
       <c r="K361" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L361" t="n">
         <v>0</v>
@@ -34127,7 +34067,7 @@
         <v>20260527</v>
       </c>
       <c r="K362" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L362" t="n">
         <v>0</v>
@@ -34220,7 +34160,7 @@
         <v>20260527</v>
       </c>
       <c r="K363" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L363" t="n">
         <v>0</v>
@@ -34313,7 +34253,7 @@
         <v>20260527</v>
       </c>
       <c r="K364" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L364" t="n">
         <v>0</v>
@@ -34406,7 +34346,7 @@
         <v>20260527</v>
       </c>
       <c r="K365" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L365" t="n">
         <v>0</v>
@@ -34499,7 +34439,7 @@
         <v>20260527</v>
       </c>
       <c r="K366" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L366" t="n">
         <v>0</v>
@@ -34592,7 +34532,7 @@
         <v>20260527</v>
       </c>
       <c r="K367" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L367" t="n">
         <v>0</v>
@@ -34685,7 +34625,7 @@
         <v>20260527</v>
       </c>
       <c r="K368" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L368" t="n">
         <v>0</v>
@@ -34778,7 +34718,7 @@
         <v>20260527</v>
       </c>
       <c r="K369" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L369" t="n">
         <v>0</v>
@@ -34871,7 +34811,7 @@
         <v>20260527</v>
       </c>
       <c r="K370" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L370" t="n">
         <v>0</v>
@@ -34964,7 +34904,7 @@
         <v>20260527</v>
       </c>
       <c r="K371" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L371" t="n">
         <v>0</v>
@@ -35057,7 +34997,7 @@
         <v>20260527</v>
       </c>
       <c r="K372" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L372" t="n">
         <v>0</v>
@@ -35150,7 +35090,7 @@
         <v>20260527</v>
       </c>
       <c r="K373" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L373" t="n">
         <v>0</v>
@@ -35243,7 +35183,7 @@
         <v>20260527</v>
       </c>
       <c r="K374" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L374" t="n">
         <v>0</v>
@@ -35336,7 +35276,7 @@
         <v>20260527</v>
       </c>
       <c r="K375" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L375" t="n">
         <v>0</v>
@@ -35429,7 +35369,7 @@
         <v>20260527</v>
       </c>
       <c r="K376" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
@@ -35522,7 +35462,7 @@
         <v>20260527</v>
       </c>
       <c r="K377" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L377" t="n">
         <v>0</v>
@@ -35615,7 +35555,7 @@
         <v>20260527</v>
       </c>
       <c r="K378" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L378" t="n">
         <v>0</v>
@@ -35708,7 +35648,7 @@
         <v>20260527</v>
       </c>
       <c r="K379" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L379" t="n">
         <v>0</v>
@@ -35801,7 +35741,7 @@
         <v>20260527</v>
       </c>
       <c r="K380" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L380" t="n">
         <v>0</v>
@@ -35894,7 +35834,7 @@
         <v>20260527</v>
       </c>
       <c r="K381" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L381" t="n">
         <v>0</v>
@@ -35987,7 +35927,7 @@
         <v>20260527</v>
       </c>
       <c r="K382" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L382" t="n">
         <v>0</v>
@@ -36080,7 +36020,7 @@
         <v>20260527</v>
       </c>
       <c r="K383" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L383" t="n">
         <v>0</v>
@@ -36173,7 +36113,7 @@
         <v>20260527</v>
       </c>
       <c r="K384" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L384" t="n">
         <v>0</v>
@@ -36266,7 +36206,7 @@
         <v>20260527</v>
       </c>
       <c r="K385" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L385" t="n">
         <v>0</v>
@@ -36359,7 +36299,7 @@
         <v>20260527</v>
       </c>
       <c r="K386" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L386" t="n">
         <v>0</v>
@@ -36452,7 +36392,7 @@
         <v>20260527</v>
       </c>
       <c r="K387" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L387" t="n">
         <v>0</v>
@@ -36545,7 +36485,7 @@
         <v>20260527</v>
       </c>
       <c r="K388" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L388" t="n">
         <v>0</v>
@@ -36638,7 +36578,7 @@
         <v>20260527</v>
       </c>
       <c r="K389" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L389" t="n">
         <v>0</v>
@@ -36731,7 +36671,7 @@
         <v>20260527</v>
       </c>
       <c r="K390" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L390" t="n">
         <v>0</v>
@@ -36824,7 +36764,7 @@
         <v>20260527</v>
       </c>
       <c r="K391" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L391" t="n">
         <v>0</v>
@@ -36917,7 +36857,7 @@
         <v>20260527</v>
       </c>
       <c r="K392" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L392" t="n">
         <v>0</v>
@@ -37010,7 +36950,7 @@
         <v>20260527</v>
       </c>
       <c r="K393" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L393" t="n">
         <v>0</v>
@@ -37103,7 +37043,7 @@
         <v>20260527</v>
       </c>
       <c r="K394" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L394" t="n">
         <v>0</v>
@@ -37196,7 +37136,7 @@
         <v>20260527</v>
       </c>
       <c r="K395" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L395" t="n">
         <v>0</v>
@@ -37289,7 +37229,7 @@
         <v>20260527</v>
       </c>
       <c r="K396" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L396" t="n">
         <v>0</v>
@@ -37382,7 +37322,7 @@
         <v>20260527</v>
       </c>
       <c r="K397" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L397" t="n">
         <v>0</v>
@@ -37475,7 +37415,7 @@
         <v>20260527</v>
       </c>
       <c r="K398" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L398" t="n">
         <v>0</v>
@@ -37568,7 +37508,7 @@
         <v>20260527</v>
       </c>
       <c r="K399" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L399" t="n">
         <v>0</v>
@@ -37661,7 +37601,7 @@
         <v>20260527</v>
       </c>
       <c r="K400" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L400" t="n">
         <v>0</v>
@@ -37754,7 +37694,7 @@
         <v>20260527</v>
       </c>
       <c r="K401" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L401" t="n">
         <v>0</v>
@@ -37847,7 +37787,7 @@
         <v>20260527</v>
       </c>
       <c r="K402" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L402" t="n">
         <v>0</v>
@@ -37940,7 +37880,7 @@
         <v>20260527</v>
       </c>
       <c r="K403" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L403" t="n">
         <v>0</v>
@@ -38033,7 +37973,7 @@
         <v>20260527</v>
       </c>
       <c r="K404" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L404" t="n">
         <v>0</v>
@@ -38126,7 +38066,7 @@
         <v>20260527</v>
       </c>
       <c r="K405" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L405" t="n">
         <v>0</v>
@@ -38219,7 +38159,7 @@
         <v>20260527</v>
       </c>
       <c r="K406" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L406" t="n">
         <v>0</v>
@@ -38312,7 +38252,7 @@
         <v>20260527</v>
       </c>
       <c r="K407" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L407" t="n">
         <v>0</v>
@@ -38405,7 +38345,7 @@
         <v>20260527</v>
       </c>
       <c r="K408" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L408" t="n">
         <v>0</v>
@@ -38498,7 +38438,7 @@
         <v>20260527</v>
       </c>
       <c r="K409" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L409" t="n">
         <v>0</v>
@@ -38591,7 +38531,7 @@
         <v>20260527</v>
       </c>
       <c r="K410" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L410" t="n">
         <v>0</v>
@@ -38684,7 +38624,7 @@
         <v>20260527</v>
       </c>
       <c r="K411" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L411" t="n">
         <v>0</v>
@@ -38777,7 +38717,7 @@
         <v>20260527</v>
       </c>
       <c r="K412" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L412" t="n">
         <v>0</v>
@@ -38870,7 +38810,7 @@
         <v>20260527</v>
       </c>
       <c r="K413" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L413" t="n">
         <v>0</v>
@@ -38963,7 +38903,7 @@
         <v>20260527</v>
       </c>
       <c r="K414" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L414" t="n">
         <v>0</v>
@@ -39056,7 +38996,7 @@
         <v>20260527</v>
       </c>
       <c r="K415" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L415" t="n">
         <v>0</v>
@@ -39149,7 +39089,7 @@
         <v>20260527</v>
       </c>
       <c r="K416" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L416" t="n">
         <v>0</v>
@@ -39242,7 +39182,7 @@
         <v>20260527</v>
       </c>
       <c r="K417" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L417" t="n">
         <v>0</v>
@@ -39335,7 +39275,7 @@
         <v>20260527</v>
       </c>
       <c r="K418" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L418" t="n">
         <v>0</v>
@@ -39428,7 +39368,7 @@
         <v>20260527</v>
       </c>
       <c r="K419" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L419" t="n">
         <v>0</v>
@@ -39521,7 +39461,7 @@
         <v>20260527</v>
       </c>
       <c r="K420" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L420" t="n">
         <v>0</v>
@@ -39614,7 +39554,7 @@
         <v>20260527</v>
       </c>
       <c r="K421" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L421" t="n">
         <v>0</v>
@@ -39707,7 +39647,7 @@
         <v>20260527</v>
       </c>
       <c r="K422" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L422" t="n">
         <v>0</v>
@@ -39800,7 +39740,7 @@
         <v>20260527</v>
       </c>
       <c r="K423" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L423" t="n">
         <v>0</v>
@@ -39893,7 +39833,7 @@
         <v>20260527</v>
       </c>
       <c r="K424" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L424" t="n">
         <v>0</v>
@@ -39998,7 +39938,7 @@
         <v>20260527</v>
       </c>
       <c r="K425" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L425" t="n">
         <v>0</v>
@@ -40103,7 +40043,7 @@
         <v>20260527</v>
       </c>
       <c r="K426" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L426" t="n">
         <v>0</v>
@@ -40208,7 +40148,7 @@
         <v>20260527</v>
       </c>
       <c r="K427" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L427" t="n">
         <v>0</v>
@@ -40313,7 +40253,7 @@
         <v>20260527</v>
       </c>
       <c r="K428" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L428" t="n">
         <v>0</v>
@@ -40418,7 +40358,7 @@
         <v>20260527</v>
       </c>
       <c r="K429" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L429" t="n">
         <v>0</v>
@@ -40523,7 +40463,7 @@
         <v>20260527</v>
       </c>
       <c r="K430" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L430" t="n">
         <v>0</v>
@@ -40628,7 +40568,7 @@
         <v>20260527</v>
       </c>
       <c r="K431" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L431" t="n">
         <v>1800</v>
@@ -40733,7 +40673,7 @@
         <v>20260527</v>
       </c>
       <c r="K432" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L432" t="n">
         <v>1800</v>
@@ -40838,7 +40778,7 @@
         <v>20260527</v>
       </c>
       <c r="K433" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L433" t="n">
         <v>1800</v>
@@ -40943,7 +40883,7 @@
         <v>20260527</v>
       </c>
       <c r="K434" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L434" t="n">
         <v>1800</v>
@@ -41048,7 +40988,7 @@
         <v>20260527</v>
       </c>
       <c r="K435" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L435" t="n">
         <v>1800</v>
@@ -41153,7 +41093,7 @@
         <v>20260527</v>
       </c>
       <c r="K436" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L436" t="n">
         <v>0</v>
@@ -41246,7 +41186,7 @@
         <v>20260527</v>
       </c>
       <c r="K437" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L437" t="n">
         <v>0</v>
@@ -41339,7 +41279,7 @@
         <v>20260527</v>
       </c>
       <c r="K438" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L438" t="n">
         <v>0</v>
@@ -41432,7 +41372,7 @@
         <v>20260527</v>
       </c>
       <c r="K439" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L439" t="n">
         <v>0</v>
@@ -41525,7 +41465,7 @@
         <v>20260527</v>
       </c>
       <c r="K440" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L440" t="n">
         <v>0</v>
@@ -41618,7 +41558,7 @@
         <v>20260527</v>
       </c>
       <c r="K441" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L441" t="n">
         <v>0</v>
@@ -41711,7 +41651,7 @@
         <v>20260527</v>
       </c>
       <c r="K442" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L442" t="n">
         <v>0</v>
@@ -41804,7 +41744,7 @@
         <v>20260527</v>
       </c>
       <c r="K443" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L443" t="n">
         <v>0</v>
@@ -41897,7 +41837,7 @@
         <v>20260527</v>
       </c>
       <c r="K444" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L444" t="n">
         <v>0</v>
@@ -41990,7 +41930,7 @@
         <v>20260527</v>
       </c>
       <c r="K445" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L445" t="n">
         <v>0</v>
@@ -42083,7 +42023,7 @@
         <v>20260527</v>
       </c>
       <c r="K446" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L446" t="n">
         <v>0</v>
@@ -42176,7 +42116,7 @@
         <v>20260527</v>
       </c>
       <c r="K447" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L447" t="n">
         <v>0</v>
@@ -42269,7 +42209,7 @@
         <v>20260527</v>
       </c>
       <c r="K448" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L448" t="n">
         <v>0</v>
@@ -42362,7 +42302,7 @@
         <v>20260527</v>
       </c>
       <c r="K449" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L449" t="n">
         <v>0</v>
@@ -42455,7 +42395,7 @@
         <v>20260527</v>
       </c>
       <c r="K450" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L450" t="n">
         <v>0</v>
@@ -42548,7 +42488,7 @@
         <v>20260527</v>
       </c>
       <c r="K451" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L451" t="n">
         <v>0</v>
@@ -42641,7 +42581,7 @@
         <v>20260527</v>
       </c>
       <c r="K452" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L452" t="n">
         <v>600</v>
@@ -42734,7 +42674,7 @@
         <v>20260527</v>
       </c>
       <c r="K453" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L453" t="n">
         <v>600</v>
@@ -42827,7 +42767,7 @@
         <v>20260527</v>
       </c>
       <c r="K454" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L454" t="n">
         <v>600</v>
@@ -42920,7 +42860,7 @@
         <v>20260527</v>
       </c>
       <c r="K455" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L455" t="n">
         <v>600</v>
@@ -43013,7 +42953,7 @@
         <v>20260527</v>
       </c>
       <c r="K456" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L456" t="n">
         <v>0</v>
@@ -43106,7 +43046,7 @@
         <v>20260527</v>
       </c>
       <c r="K457" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L457" t="n">
         <v>0</v>
@@ -43199,7 +43139,7 @@
         <v>20260527</v>
       </c>
       <c r="K458" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L458" t="n">
         <v>0</v>
@@ -43292,7 +43232,7 @@
         <v>20260527</v>
       </c>
       <c r="K459" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L459" t="n">
         <v>0</v>
@@ -43385,7 +43325,7 @@
         <v>20260527</v>
       </c>
       <c r="K460" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L460" t="n">
         <v>0</v>
@@ -43478,7 +43418,7 @@
         <v>20260527</v>
       </c>
       <c r="K461" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L461" t="n">
         <v>0</v>
@@ -43571,7 +43511,7 @@
         <v>20260527</v>
       </c>
       <c r="K462" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L462" t="n">
         <v>0</v>
@@ -43664,7 +43604,7 @@
         <v>20260527</v>
       </c>
       <c r="K463" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L463" t="n">
         <v>0</v>
@@ -43757,7 +43697,7 @@
         <v>20260527</v>
       </c>
       <c r="K464" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L464" t="n">
         <v>600</v>
@@ -43850,7 +43790,7 @@
         <v>20260527</v>
       </c>
       <c r="K465" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L465" t="n">
         <v>600</v>
@@ -43943,7 +43883,7 @@
         <v>20260527</v>
       </c>
       <c r="K466" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L466" t="n">
         <v>600</v>
@@ -44036,7 +43976,7 @@
         <v>20260527</v>
       </c>
       <c r="K467" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L467" t="n">
         <v>600</v>
@@ -44129,7 +44069,7 @@
         <v>20260527</v>
       </c>
       <c r="K468" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L468" t="n">
         <v>0</v>
@@ -44222,7 +44162,7 @@
         <v>20260527</v>
       </c>
       <c r="K469" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L469" t="n">
         <v>0</v>
@@ -44315,7 +44255,7 @@
         <v>20260527</v>
       </c>
       <c r="K470" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L470" t="n">
         <v>0</v>
@@ -44408,7 +44348,7 @@
         <v>20260527</v>
       </c>
       <c r="K471" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L471" t="n">
         <v>0</v>
@@ -44501,7 +44441,7 @@
         <v>20260527</v>
       </c>
       <c r="K472" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L472" t="n">
         <v>0</v>
@@ -44594,7 +44534,7 @@
         <v>20260527</v>
       </c>
       <c r="K473" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L473" t="n">
         <v>0</v>
@@ -44699,7 +44639,7 @@
         <v>20260527</v>
       </c>
       <c r="K474" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L474" t="n">
         <v>0</v>
@@ -44804,7 +44744,7 @@
         <v>20260527</v>
       </c>
       <c r="K475" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L475" t="n">
         <v>900</v>
@@ -44909,7 +44849,7 @@
         <v>20260527</v>
       </c>
       <c r="K476" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L476" t="n">
         <v>900</v>
@@ -45014,7 +44954,7 @@
         <v>20260527</v>
       </c>
       <c r="K477" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L477" t="n">
         <v>900</v>
@@ -45119,7 +45059,7 @@
         <v>20260527</v>
       </c>
       <c r="K478" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L478" t="n">
         <v>0</v>
@@ -45212,7 +45152,7 @@
         <v>20260527</v>
       </c>
       <c r="K479" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L479" t="n">
         <v>0</v>
@@ -45305,7 +45245,7 @@
         <v>20260527</v>
       </c>
       <c r="K480" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L480" t="n">
         <v>0</v>
@@ -45398,7 +45338,7 @@
         <v>20260527</v>
       </c>
       <c r="K481" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L481" t="n">
         <v>0</v>
@@ -45491,7 +45431,7 @@
         <v>20260527</v>
       </c>
       <c r="K482" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L482" t="n">
         <v>0</v>
@@ -45584,7 +45524,7 @@
         <v>20260527</v>
       </c>
       <c r="K483" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L483" t="n">
         <v>0</v>
@@ -45677,7 +45617,7 @@
         <v>20260527</v>
       </c>
       <c r="K484" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L484" t="n">
         <v>900</v>
@@ -45770,7 +45710,7 @@
         <v>20260527</v>
       </c>
       <c r="K485" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L485" t="n">
         <v>900</v>
@@ -45863,7 +45803,7 @@
         <v>20260527</v>
       </c>
       <c r="K486" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L486" t="n">
         <v>600</v>
@@ -45956,7 +45896,7 @@
         <v>20260527</v>
       </c>
       <c r="K487" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L487" t="n">
         <v>300</v>
@@ -46049,7 +45989,7 @@
         <v>20260527</v>
       </c>
       <c r="K488" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L488" t="n">
         <v>0</v>
@@ -46142,7 +46082,7 @@
         <v>20260527</v>
       </c>
       <c r="K489" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L489" t="n">
         <v>0</v>
@@ -46235,7 +46175,7 @@
         <v>20260527</v>
       </c>
       <c r="K490" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L490" t="n">
         <v>0</v>
@@ -46328,7 +46268,7 @@
         <v>20260527</v>
       </c>
       <c r="K491" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L491" t="n">
         <v>0</v>
@@ -46421,7 +46361,7 @@
         <v>20260527</v>
       </c>
       <c r="K492" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L492" t="n">
         <v>0</v>
@@ -46526,7 +46466,7 @@
         <v>20260527</v>
       </c>
       <c r="K493" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L493" t="n">
         <v>0</v>
@@ -46631,7 +46571,7 @@
         <v>20260527</v>
       </c>
       <c r="K494" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L494" t="n">
         <v>900</v>
@@ -46736,7 +46676,7 @@
         <v>20260527</v>
       </c>
       <c r="K495" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L495" t="n">
         <v>600</v>
@@ -46841,7 +46781,7 @@
         <v>20260527</v>
       </c>
       <c r="K496" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L496" t="n">
         <v>0</v>
@@ -46934,7 +46874,7 @@
         <v>20260527</v>
       </c>
       <c r="K497" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L497" t="n">
         <v>0</v>
@@ -47027,7 +46967,7 @@
         <v>20260527</v>
       </c>
       <c r="K498" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L498" t="n">
         <v>0</v>
@@ -47120,7 +47060,7 @@
         <v>20260527</v>
       </c>
       <c r="K499" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L499" t="n">
         <v>0</v>
@@ -47213,7 +47153,7 @@
         <v>20260527</v>
       </c>
       <c r="K500" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L500" t="n">
         <v>0</v>
@@ -47318,7 +47258,7 @@
         <v>20260527</v>
       </c>
       <c r="K501" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L501" t="n">
         <v>0</v>
@@ -47423,7 +47363,7 @@
         <v>20260527</v>
       </c>
       <c r="K502" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L502" t="n">
         <v>900</v>
@@ -47528,7 +47468,7 @@
         <v>20260527</v>
       </c>
       <c r="K503" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L503" t="n">
         <v>900</v>
@@ -47633,7 +47573,7 @@
         <v>20260527</v>
       </c>
       <c r="K504" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L504" t="n">
         <v>0</v>
@@ -47726,7 +47666,7 @@
         <v>20260527</v>
       </c>
       <c r="K505" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L505" t="n">
         <v>0</v>
@@ -47819,7 +47759,7 @@
         <v>20260527</v>
       </c>
       <c r="K506" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L506" t="n">
         <v>0</v>
@@ -47912,7 +47852,7 @@
         <v>20260527</v>
       </c>
       <c r="K507" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L507" t="n">
         <v>0</v>
@@ -48005,7 +47945,7 @@
         <v>20260527</v>
       </c>
       <c r="K508" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L508" t="n">
         <v>0</v>
@@ -48110,7 +48050,7 @@
         <v>20260527</v>
       </c>
       <c r="K509" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L509" t="n">
         <v>0</v>
@@ -48215,7 +48155,7 @@
         <v>20260527</v>
       </c>
       <c r="K510" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L510" t="n">
         <v>0</v>
@@ -48320,7 +48260,7 @@
         <v>20260527</v>
       </c>
       <c r="K511" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L511" t="n">
         <v>0</v>
@@ -48425,7 +48365,7 @@
         <v>20260527</v>
       </c>
       <c r="K512" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L512" t="n">
         <v>0</v>
@@ -48518,7 +48458,7 @@
         <v>20260527</v>
       </c>
       <c r="K513" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L513" t="n">
         <v>0</v>
@@ -48611,7 +48551,7 @@
         <v>20260527</v>
       </c>
       <c r="K514" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L514" t="n">
         <v>300</v>
@@ -48704,7 +48644,7 @@
         <v>20260527</v>
       </c>
       <c r="K515" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L515" t="n">
         <v>300</v>
@@ -48797,7 +48737,7 @@
         <v>20260527</v>
       </c>
       <c r="K516" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L516" t="n">
         <v>300</v>
@@ -48890,7 +48830,7 @@
         <v>20260527</v>
       </c>
       <c r="K517" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L517" t="n">
         <v>300</v>
@@ -48983,7 +48923,7 @@
         <v>20260527</v>
       </c>
       <c r="K518" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L518" t="n">
         <v>300</v>
@@ -49076,7 +49016,7 @@
         <v>20260527</v>
       </c>
       <c r="K519" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L519" t="n">
         <v>0</v>
@@ -49181,7 +49121,7 @@
         <v>20260527</v>
       </c>
       <c r="K520" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L520" t="n">
         <v>0</v>
@@ -49286,7 +49226,7 @@
         <v>20260527</v>
       </c>
       <c r="K521" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L521" t="n">
         <v>0</v>
@@ -49391,7 +49331,7 @@
         <v>20260527</v>
       </c>
       <c r="K522" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L522" t="n">
         <v>0</v>
@@ -49496,7 +49436,7 @@
         <v>20260527</v>
       </c>
       <c r="K523" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L523" t="n">
         <v>0</v>
@@ -49601,7 +49541,7 @@
         <v>20260527</v>
       </c>
       <c r="K524" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L524" t="n">
         <v>0</v>
@@ -49706,7 +49646,7 @@
         <v>20260527</v>
       </c>
       <c r="K525" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L525" t="n">
         <v>0</v>
@@ -49811,7 +49751,7 @@
         <v>20260527</v>
       </c>
       <c r="K526" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L526" t="n">
         <v>0</v>
@@ -49904,7 +49844,7 @@
         <v>20260527</v>
       </c>
       <c r="K527" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L527" t="n">
         <v>0</v>
@@ -49997,7 +49937,7 @@
         <v>20260527</v>
       </c>
       <c r="K528" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L528" t="n">
         <v>0</v>
@@ -50090,7 +50030,7 @@
         <v>20260527</v>
       </c>
       <c r="K529" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L529" t="n">
         <v>0</v>
@@ -50183,7 +50123,7 @@
         <v>20260527</v>
       </c>
       <c r="K530" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L530" t="n">
         <v>0</v>
@@ -50288,7 +50228,7 @@
         <v>20260527</v>
       </c>
       <c r="K531" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L531" t="n">
         <v>0</v>
@@ -50393,7 +50333,7 @@
         <v>20260527</v>
       </c>
       <c r="K532" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L532" t="n">
         <v>0</v>
@@ -50498,7 +50438,7 @@
         <v>20260527</v>
       </c>
       <c r="K533" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L533" t="n">
         <v>0</v>
@@ -50603,7 +50543,7 @@
         <v>20260527</v>
       </c>
       <c r="K534" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L534" t="n">
         <v>0</v>
@@ -50696,7 +50636,7 @@
         <v>20260527</v>
       </c>
       <c r="K535" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L535" t="n">
         <v>0</v>
@@ -50789,7 +50729,7 @@
         <v>20260527</v>
       </c>
       <c r="K536" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L536" t="n">
         <v>0</v>
@@ -50882,7 +50822,7 @@
         <v>20260527</v>
       </c>
       <c r="K537" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L537" t="n">
         <v>0</v>
@@ -50975,7 +50915,7 @@
         <v>20260527</v>
       </c>
       <c r="K538" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L538" t="n">
         <v>0</v>
@@ -51068,7 +51008,7 @@
         <v>20260527</v>
       </c>
       <c r="K539" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L539" t="n">
         <v>0</v>
@@ -51161,7 +51101,7 @@
         <v>20260527</v>
       </c>
       <c r="K540" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L540" t="n">
         <v>0</v>
@@ -51254,7 +51194,7 @@
         <v>20260527</v>
       </c>
       <c r="K541" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L541" t="n">
         <v>0</v>
@@ -51347,7 +51287,7 @@
         <v>20260527</v>
       </c>
       <c r="K542" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L542" t="n">
         <v>0</v>
@@ -51440,7 +51380,7 @@
         <v>20260527</v>
       </c>
       <c r="K543" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L543" t="n">
         <v>0</v>
@@ -51533,7 +51473,7 @@
         <v>20260527</v>
       </c>
       <c r="K544" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L544" t="n">
         <v>0</v>
@@ -51626,7 +51566,7 @@
         <v>20260527</v>
       </c>
       <c r="K545" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L545" t="n">
         <v>0</v>
@@ -51719,7 +51659,7 @@
         <v>20260527</v>
       </c>
       <c r="K546" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L546" t="n">
         <v>0</v>
@@ -51812,7 +51752,7 @@
         <v>20260527</v>
       </c>
       <c r="K547" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L547" t="n">
         <v>0</v>
@@ -51905,7 +51845,7 @@
         <v>20260527</v>
       </c>
       <c r="K548" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L548" t="n">
         <v>300</v>
@@ -51998,7 +51938,7 @@
         <v>20260527</v>
       </c>
       <c r="K549" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L549" t="n">
         <v>300</v>
@@ -52091,7 +52031,7 @@
         <v>20260527</v>
       </c>
       <c r="K550" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L550" t="n">
         <v>300</v>
@@ -52184,7 +52124,7 @@
         <v>20260527</v>
       </c>
       <c r="K551" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L551" t="n">
         <v>0</v>
@@ -52277,7 +52217,7 @@
         <v>20260527</v>
       </c>
       <c r="K552" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L552" t="n">
         <v>0</v>
@@ -52370,7 +52310,7 @@
         <v>20260527</v>
       </c>
       <c r="K553" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L553" t="n">
         <v>0</v>
@@ -52463,7 +52403,7 @@
         <v>20260527</v>
       </c>
       <c r="K554" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L554" t="n">
         <v>0</v>
@@ -52556,7 +52496,7 @@
         <v>20260527</v>
       </c>
       <c r="K555" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L555" t="n">
         <v>0</v>
@@ -52649,7 +52589,7 @@
         <v>20260527</v>
       </c>
       <c r="K556" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L556" t="n">
         <v>900</v>
@@ -52742,7 +52682,7 @@
         <v>20260527</v>
       </c>
       <c r="K557" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L557" t="n">
         <v>900</v>
@@ -52835,7 +52775,7 @@
         <v>20260527</v>
       </c>
       <c r="K558" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L558" t="n">
         <v>900</v>
@@ -52928,7 +52868,7 @@
         <v>20260527</v>
       </c>
       <c r="K559" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L559" t="n">
         <v>900</v>
@@ -53021,7 +52961,7 @@
         <v>20260527</v>
       </c>
       <c r="K560" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L560" t="n">
         <v>0</v>
@@ -53114,7 +53054,7 @@
         <v>20260527</v>
       </c>
       <c r="K561" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L561" t="n">
         <v>300</v>
@@ -53207,7 +53147,7 @@
         <v>20260527</v>
       </c>
       <c r="K562" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L562" t="n">
         <v>600</v>
@@ -53300,7 +53240,7 @@
         <v>20260527</v>
       </c>
       <c r="K563" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L563" t="n">
         <v>600</v>
@@ -53393,7 +53333,7 @@
         <v>20260527</v>
       </c>
       <c r="K564" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L564" t="n">
         <v>600</v>
@@ -53486,7 +53426,7 @@
         <v>20260527</v>
       </c>
       <c r="K565" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L565" t="n">
         <v>600</v>
@@ -53579,7 +53519,7 @@
         <v>20260527</v>
       </c>
       <c r="K566" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L566" t="n">
         <v>600</v>
@@ -53672,7 +53612,7 @@
         <v>20260527</v>
       </c>
       <c r="K567" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L567" t="n">
         <v>600</v>
@@ -53765,7 +53705,7 @@
         <v>20260527</v>
       </c>
       <c r="K568" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L568" t="n">
         <v>600</v>
@@ -53858,7 +53798,7 @@
         <v>20260527</v>
       </c>
       <c r="K569" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L569" t="n">
         <v>600</v>
@@ -53951,7 +53891,7 @@
         <v>20260527</v>
       </c>
       <c r="K570" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L570" t="n">
         <v>0</v>
@@ -53977,11 +53917,11 @@
       </c>
       <c r="R570" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S570" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T570" t="b">
         <v>0</v>
@@ -54056,7 +53996,7 @@
         <v>20260527</v>
       </c>
       <c r="K571" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L571" t="n">
         <v>0</v>
@@ -54082,11 +54022,11 @@
       </c>
       <c r="R571" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S571" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T571" t="b">
         <v>0</v>
@@ -54161,7 +54101,7 @@
         <v>20260527</v>
       </c>
       <c r="K572" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L572" t="n">
         <v>900</v>
@@ -54187,11 +54127,11 @@
       </c>
       <c r="R572" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S572" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T572" t="b">
         <v>0</v>
@@ -54266,7 +54206,7 @@
         <v>20260527</v>
       </c>
       <c r="K573" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L573" t="n">
         <v>900</v>
@@ -54292,11 +54232,11 @@
       </c>
       <c r="R573" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S573" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T573" t="b">
         <v>0</v>
@@ -54371,7 +54311,7 @@
         <v>20260527</v>
       </c>
       <c r="K574" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L574" t="n">
         <v>900</v>
@@ -54397,11 +54337,11 @@
       </c>
       <c r="R574" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S574" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T574" t="b">
         <v>0</v>
@@ -54476,7 +54416,7 @@
         <v>20260527</v>
       </c>
       <c r="K575" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L575" t="n">
         <v>900</v>
@@ -54502,11 +54442,11 @@
       </c>
       <c r="R575" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S575" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T575" t="b">
         <v>0</v>
@@ -54581,7 +54521,7 @@
         <v>20260527</v>
       </c>
       <c r="K576" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L576" t="n">
         <v>900</v>
@@ -54607,11 +54547,11 @@
       </c>
       <c r="R576" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S576" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T576" t="b">
         <v>0</v>
@@ -54686,7 +54626,7 @@
         <v>20260527</v>
       </c>
       <c r="K577" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L577" t="n">
         <v>900</v>
@@ -54712,11 +54652,11 @@
       </c>
       <c r="R577" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S577" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T577" t="b">
         <v>0</v>
@@ -54791,7 +54731,7 @@
         <v>20260527</v>
       </c>
       <c r="K578" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L578" t="n">
         <v>900</v>
@@ -54817,11 +54757,11 @@
       </c>
       <c r="R578" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S578" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T578" t="b">
         <v>0</v>
@@ -54896,7 +54836,7 @@
         <v>20260527</v>
       </c>
       <c r="K579" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L579" t="n">
         <v>900</v>
@@ -54922,11 +54862,11 @@
       </c>
       <c r="R579" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S579" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T579" t="b">
         <v>0</v>
@@ -55001,7 +54941,7 @@
         <v>20260527</v>
       </c>
       <c r="K580" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L580" t="n">
         <v>0</v>
@@ -55094,7 +55034,7 @@
         <v>20260527</v>
       </c>
       <c r="K581" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L581" t="n">
         <v>0</v>
@@ -55187,7 +55127,7 @@
         <v>20260527</v>
       </c>
       <c r="K582" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L582" t="n">
         <v>0</v>
@@ -55280,7 +55220,7 @@
         <v>20260527</v>
       </c>
       <c r="K583" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L583" t="n">
         <v>0</v>
@@ -55373,7 +55313,7 @@
         <v>20260527</v>
       </c>
       <c r="K584" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L584" t="n">
         <v>300</v>
@@ -55466,7 +55406,7 @@
         <v>20260527</v>
       </c>
       <c r="K585" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L585" t="n">
         <v>600</v>
@@ -55559,7 +55499,7 @@
         <v>20260527</v>
       </c>
       <c r="K586" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L586" t="n">
         <v>600</v>
@@ -55652,7 +55592,7 @@
         <v>20260527</v>
       </c>
       <c r="K587" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L587" t="n">
         <v>600</v>
@@ -55745,7 +55685,7 @@
         <v>20260527</v>
       </c>
       <c r="K588" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L588" t="n">
         <v>300</v>
@@ -55838,7 +55778,7 @@
         <v>20260527</v>
       </c>
       <c r="K589" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L589" t="n">
         <v>300</v>
@@ -55931,7 +55871,7 @@
         <v>20260527</v>
       </c>
       <c r="K590" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L590" t="n">
         <v>300</v>
@@ -56024,7 +55964,7 @@
         <v>20260527</v>
       </c>
       <c r="K591" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L591" t="n">
         <v>300</v>
@@ -56117,7 +56057,7 @@
         <v>20260527</v>
       </c>
       <c r="K592" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L592" t="n">
         <v>300</v>
@@ -56210,7 +56150,7 @@
         <v>20260527</v>
       </c>
       <c r="K593" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L593" t="n">
         <v>300</v>
@@ -56303,7 +56243,7 @@
         <v>20260527</v>
       </c>
       <c r="K594" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L594" t="n">
         <v>0</v>
@@ -56329,11 +56269,11 @@
       </c>
       <c r="R594" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S594" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T594" t="b">
         <v>0</v>
@@ -56396,7 +56336,7 @@
         <v>20260527</v>
       </c>
       <c r="K595" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L595" t="n">
         <v>0</v>
@@ -56422,11 +56362,11 @@
       </c>
       <c r="R595" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S595" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T595" t="b">
         <v>0</v>
@@ -56489,7 +56429,7 @@
         <v>20260527</v>
       </c>
       <c r="K596" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L596" t="n">
         <v>0</v>
@@ -56515,11 +56455,11 @@
       </c>
       <c r="R596" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S596" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T596" t="b">
         <v>0</v>
@@ -56582,7 +56522,7 @@
         <v>20260527</v>
       </c>
       <c r="K597" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L597" t="n">
         <v>0</v>
@@ -56608,11 +56548,11 @@
       </c>
       <c r="R597" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S597" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T597" t="b">
         <v>0</v>
@@ -56675,7 +56615,7 @@
         <v>20260527</v>
       </c>
       <c r="K598" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L598" t="n">
         <v>0</v>
@@ -56701,11 +56641,11 @@
       </c>
       <c r="R598" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S598" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T598" t="b">
         <v>0</v>
@@ -56768,7 +56708,7 @@
         <v>20260527</v>
       </c>
       <c r="K599" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L599" t="n">
         <v>0</v>
@@ -56794,11 +56734,11 @@
       </c>
       <c r="R599" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S599" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T599" t="b">
         <v>0</v>
@@ -56861,7 +56801,7 @@
         <v>20260527</v>
       </c>
       <c r="K600" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L600" t="n">
         <v>0</v>
@@ -56887,11 +56827,11 @@
       </c>
       <c r="R600" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S600" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T600" t="b">
         <v>0</v>
@@ -56954,7 +56894,7 @@
         <v>20260527</v>
       </c>
       <c r="K601" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L601" t="n">
         <v>0</v>
@@ -56980,11 +56920,11 @@
       </c>
       <c r="R601" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S601" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T601" t="b">
         <v>0</v>
@@ -57047,7 +56987,7 @@
         <v>20260527</v>
       </c>
       <c r="K602" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L602" t="n">
         <v>0</v>
@@ -57073,11 +57013,11 @@
       </c>
       <c r="R602" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S602" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T602" t="b">
         <v>0</v>
@@ -57140,7 +57080,7 @@
         <v>20260527</v>
       </c>
       <c r="K603" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L603" t="n">
         <v>0</v>
@@ -57166,11 +57106,11 @@
       </c>
       <c r="R603" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S603" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T603" t="b">
         <v>0</v>
@@ -57233,7 +57173,7 @@
         <v>20260527</v>
       </c>
       <c r="K604" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L604" t="n">
         <v>0</v>
@@ -57259,11 +57199,11 @@
       </c>
       <c r="R604" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S604" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T604" t="b">
         <v>0</v>
@@ -57326,7 +57266,7 @@
         <v>20260527</v>
       </c>
       <c r="K605" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L605" t="n">
         <v>0</v>
@@ -57352,11 +57292,11 @@
       </c>
       <c r="R605" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S605" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T605" t="b">
         <v>0</v>
@@ -57419,7 +57359,7 @@
         <v>20260527</v>
       </c>
       <c r="K606" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L606" t="n">
         <v>0</v>
@@ -57445,11 +57385,11 @@
       </c>
       <c r="R606" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>active</t>
         </is>
       </c>
       <c r="S606" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T606" t="b">
         <v>0</v>
@@ -57512,7 +57452,7 @@
         <v>20260527</v>
       </c>
       <c r="K607" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L607" t="n">
         <v>0</v>
@@ -57605,7 +57545,7 @@
         <v>20260527</v>
       </c>
       <c r="K608" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L608" t="n">
         <v>0</v>
@@ -57698,7 +57638,7 @@
         <v>20260527</v>
       </c>
       <c r="K609" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L609" t="n">
         <v>0</v>
@@ -57791,7 +57731,7 @@
         <v>20260527</v>
       </c>
       <c r="K610" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L610" t="n">
         <v>0</v>
@@ -57884,7 +57824,7 @@
         <v>20260527</v>
       </c>
       <c r="K611" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L611" t="n">
         <v>0</v>
@@ -57977,7 +57917,7 @@
         <v>20260527</v>
       </c>
       <c r="K612" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L612" t="n">
         <v>0</v>
@@ -58070,7 +58010,7 @@
         <v>20260527</v>
       </c>
       <c r="K613" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L613" t="n">
         <v>0</v>
@@ -58163,7 +58103,7 @@
         <v>20260527</v>
       </c>
       <c r="K614" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L614" t="n">
         <v>0</v>
@@ -58256,7 +58196,7 @@
         <v>20260527</v>
       </c>
       <c r="K615" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L615" t="n">
         <v>0</v>
@@ -58349,7 +58289,7 @@
         <v>20260527</v>
       </c>
       <c r="K616" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L616" t="n">
         <v>0</v>
@@ -58442,7 +58382,7 @@
         <v>20260527</v>
       </c>
       <c r="K617" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L617" t="n">
         <v>0</v>
@@ -58535,7 +58475,7 @@
         <v>20260527</v>
       </c>
       <c r="K618" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L618" t="n">
         <v>0</v>
@@ -58628,7 +58568,7 @@
         <v>20260527</v>
       </c>
       <c r="K619" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L619" t="n">
         <v>0</v>
@@ -58721,7 +58661,7 @@
         <v>20260527</v>
       </c>
       <c r="K620" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L620" t="n">
         <v>0</v>
@@ -58814,7 +58754,7 @@
         <v>20260527</v>
       </c>
       <c r="K621" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L621" t="n">
         <v>0</v>
@@ -58907,7 +58847,7 @@
         <v>20260527</v>
       </c>
       <c r="K622" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L622" t="n">
         <v>0</v>
@@ -59000,7 +58940,7 @@
         <v>20260527</v>
       </c>
       <c r="K623" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L623" t="n">
         <v>0</v>
@@ -59093,7 +59033,7 @@
         <v>20260527</v>
       </c>
       <c r="K624" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L624" t="n">
         <v>0</v>
@@ -59186,7 +59126,7 @@
         <v>20260527</v>
       </c>
       <c r="K625" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L625" t="n">
         <v>0</v>
@@ -59279,7 +59219,7 @@
         <v>20260527</v>
       </c>
       <c r="K626" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L626" t="n">
         <v>0</v>
@@ -59372,7 +59312,7 @@
         <v>20260527</v>
       </c>
       <c r="K627" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L627" t="n">
         <v>0</v>
@@ -59465,7 +59405,7 @@
         <v>20260527</v>
       </c>
       <c r="K628" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L628" t="n">
         <v>0</v>
@@ -59558,7 +59498,7 @@
         <v>20260527</v>
       </c>
       <c r="K629" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L629" t="n">
         <v>0</v>
@@ -59651,7 +59591,7 @@
         <v>20260527</v>
       </c>
       <c r="K630" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L630" t="n">
         <v>0</v>
@@ -59744,7 +59684,7 @@
         <v>20260527</v>
       </c>
       <c r="K631" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L631" t="n">
         <v>0</v>
@@ -59837,7 +59777,7 @@
         <v>20260527</v>
       </c>
       <c r="K632" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L632" t="n">
         <v>0</v>
@@ -59930,7 +59870,7 @@
         <v>20260527</v>
       </c>
       <c r="K633" t="n">
-        <v>1779872748</v>
+        <v>1779873473</v>
       </c>
       <c r="L633" t="n">
         <v>0</v>
